--- a/data/intermediate/pib.xlsx
+++ b/data/intermediate/pib.xlsx
@@ -28,22 +28,571 @@
     <t>Valor</t>
   </si>
   <si>
+    <t>Variación Anual</t>
+  </si>
+  <si>
+    <t>Valores absolutos</t>
+  </si>
+  <si>
     <t>Variación Trimestral</t>
   </si>
   <si>
-    <t>Variación Anual</t>
-  </si>
-  <si>
-    <t>Valores absolutos</t>
+    <t>736183</t>
+  </si>
+  <si>
+    <t>736181</t>
   </si>
   <si>
     <t>736182</t>
   </si>
   <si>
-    <t>736183</t>
-  </si>
-  <si>
-    <t>736181</t>
+    <t>1981/01</t>
+  </si>
+  <si>
+    <t>1981/02</t>
+  </si>
+  <si>
+    <t>1981/03</t>
+  </si>
+  <si>
+    <t>1981/04</t>
+  </si>
+  <si>
+    <t>1982/01</t>
+  </si>
+  <si>
+    <t>1982/02</t>
+  </si>
+  <si>
+    <t>1982/03</t>
+  </si>
+  <si>
+    <t>1982/04</t>
+  </si>
+  <si>
+    <t>1983/01</t>
+  </si>
+  <si>
+    <t>1983/02</t>
+  </si>
+  <si>
+    <t>1983/03</t>
+  </si>
+  <si>
+    <t>1983/04</t>
+  </si>
+  <si>
+    <t>1984/01</t>
+  </si>
+  <si>
+    <t>1984/02</t>
+  </si>
+  <si>
+    <t>1984/03</t>
+  </si>
+  <si>
+    <t>1984/04</t>
+  </si>
+  <si>
+    <t>1985/01</t>
+  </si>
+  <si>
+    <t>1985/02</t>
+  </si>
+  <si>
+    <t>1985/03</t>
+  </si>
+  <si>
+    <t>1985/04</t>
+  </si>
+  <si>
+    <t>1986/01</t>
+  </si>
+  <si>
+    <t>1986/02</t>
+  </si>
+  <si>
+    <t>1986/03</t>
+  </si>
+  <si>
+    <t>1986/04</t>
+  </si>
+  <si>
+    <t>1987/01</t>
+  </si>
+  <si>
+    <t>1987/02</t>
+  </si>
+  <si>
+    <t>1987/03</t>
+  </si>
+  <si>
+    <t>1987/04</t>
+  </si>
+  <si>
+    <t>1988/01</t>
+  </si>
+  <si>
+    <t>1988/02</t>
+  </si>
+  <si>
+    <t>1988/03</t>
+  </si>
+  <si>
+    <t>1988/04</t>
+  </si>
+  <si>
+    <t>1989/01</t>
+  </si>
+  <si>
+    <t>1989/02</t>
+  </si>
+  <si>
+    <t>1989/03</t>
+  </si>
+  <si>
+    <t>1989/04</t>
+  </si>
+  <si>
+    <t>1990/01</t>
+  </si>
+  <si>
+    <t>1990/02</t>
+  </si>
+  <si>
+    <t>1990/03</t>
+  </si>
+  <si>
+    <t>1990/04</t>
+  </si>
+  <si>
+    <t>1991/01</t>
+  </si>
+  <si>
+    <t>1991/02</t>
+  </si>
+  <si>
+    <t>1991/03</t>
+  </si>
+  <si>
+    <t>1991/04</t>
+  </si>
+  <si>
+    <t>1992/01</t>
+  </si>
+  <si>
+    <t>1992/02</t>
+  </si>
+  <si>
+    <t>1992/03</t>
+  </si>
+  <si>
+    <t>1992/04</t>
+  </si>
+  <si>
+    <t>1993/01</t>
+  </si>
+  <si>
+    <t>1993/02</t>
+  </si>
+  <si>
+    <t>1993/03</t>
+  </si>
+  <si>
+    <t>1993/04</t>
+  </si>
+  <si>
+    <t>1994/01</t>
+  </si>
+  <si>
+    <t>1994/02</t>
+  </si>
+  <si>
+    <t>1994/03</t>
+  </si>
+  <si>
+    <t>1994/04</t>
+  </si>
+  <si>
+    <t>1995/01</t>
+  </si>
+  <si>
+    <t>1995/02</t>
+  </si>
+  <si>
+    <t>1995/03</t>
+  </si>
+  <si>
+    <t>1995/04</t>
+  </si>
+  <si>
+    <t>1996/01</t>
+  </si>
+  <si>
+    <t>1996/02</t>
+  </si>
+  <si>
+    <t>1996/03</t>
+  </si>
+  <si>
+    <t>1996/04</t>
+  </si>
+  <si>
+    <t>1997/01</t>
+  </si>
+  <si>
+    <t>1997/02</t>
+  </si>
+  <si>
+    <t>1997/03</t>
+  </si>
+  <si>
+    <t>1997/04</t>
+  </si>
+  <si>
+    <t>1998/01</t>
+  </si>
+  <si>
+    <t>1998/02</t>
+  </si>
+  <si>
+    <t>1998/03</t>
+  </si>
+  <si>
+    <t>1998/04</t>
+  </si>
+  <si>
+    <t>1999/01</t>
+  </si>
+  <si>
+    <t>1999/02</t>
+  </si>
+  <si>
+    <t>1999/03</t>
+  </si>
+  <si>
+    <t>1999/04</t>
+  </si>
+  <si>
+    <t>2000/01</t>
+  </si>
+  <si>
+    <t>2000/02</t>
+  </si>
+  <si>
+    <t>2000/03</t>
+  </si>
+  <si>
+    <t>2000/04</t>
+  </si>
+  <si>
+    <t>2001/01</t>
+  </si>
+  <si>
+    <t>2001/02</t>
+  </si>
+  <si>
+    <t>2001/03</t>
+  </si>
+  <si>
+    <t>2001/04</t>
+  </si>
+  <si>
+    <t>2002/01</t>
+  </si>
+  <si>
+    <t>2002/02</t>
+  </si>
+  <si>
+    <t>2002/03</t>
+  </si>
+  <si>
+    <t>2002/04</t>
+  </si>
+  <si>
+    <t>2003/01</t>
+  </si>
+  <si>
+    <t>2003/02</t>
+  </si>
+  <si>
+    <t>2003/03</t>
+  </si>
+  <si>
+    <t>2003/04</t>
+  </si>
+  <si>
+    <t>2004/01</t>
+  </si>
+  <si>
+    <t>2004/02</t>
+  </si>
+  <si>
+    <t>2004/03</t>
+  </si>
+  <si>
+    <t>2004/04</t>
+  </si>
+  <si>
+    <t>2005/01</t>
+  </si>
+  <si>
+    <t>2005/02</t>
+  </si>
+  <si>
+    <t>2005/03</t>
+  </si>
+  <si>
+    <t>2005/04</t>
+  </si>
+  <si>
+    <t>2006/01</t>
+  </si>
+  <si>
+    <t>2006/02</t>
+  </si>
+  <si>
+    <t>2006/03</t>
+  </si>
+  <si>
+    <t>2006/04</t>
+  </si>
+  <si>
+    <t>2007/01</t>
+  </si>
+  <si>
+    <t>2007/02</t>
+  </si>
+  <si>
+    <t>2007/03</t>
+  </si>
+  <si>
+    <t>2007/04</t>
+  </si>
+  <si>
+    <t>2008/01</t>
+  </si>
+  <si>
+    <t>2008/02</t>
+  </si>
+  <si>
+    <t>2008/03</t>
+  </si>
+  <si>
+    <t>2008/04</t>
+  </si>
+  <si>
+    <t>2009/01</t>
+  </si>
+  <si>
+    <t>2009/02</t>
+  </si>
+  <si>
+    <t>2009/03</t>
+  </si>
+  <si>
+    <t>2009/04</t>
+  </si>
+  <si>
+    <t>2010/01</t>
+  </si>
+  <si>
+    <t>2010/02</t>
+  </si>
+  <si>
+    <t>2010/03</t>
+  </si>
+  <si>
+    <t>2010/04</t>
+  </si>
+  <si>
+    <t>2011/01</t>
+  </si>
+  <si>
+    <t>2011/02</t>
+  </si>
+  <si>
+    <t>2011/03</t>
+  </si>
+  <si>
+    <t>2011/04</t>
+  </si>
+  <si>
+    <t>2012/01</t>
+  </si>
+  <si>
+    <t>2012/02</t>
+  </si>
+  <si>
+    <t>2012/03</t>
+  </si>
+  <si>
+    <t>2012/04</t>
+  </si>
+  <si>
+    <t>2013/01</t>
+  </si>
+  <si>
+    <t>2013/02</t>
+  </si>
+  <si>
+    <t>2013/03</t>
+  </si>
+  <si>
+    <t>2013/04</t>
+  </si>
+  <si>
+    <t>2014/01</t>
+  </si>
+  <si>
+    <t>2014/02</t>
+  </si>
+  <si>
+    <t>2014/03</t>
+  </si>
+  <si>
+    <t>2014/04</t>
+  </si>
+  <si>
+    <t>2015/01</t>
+  </si>
+  <si>
+    <t>2015/02</t>
+  </si>
+  <si>
+    <t>2015/03</t>
+  </si>
+  <si>
+    <t>2015/04</t>
+  </si>
+  <si>
+    <t>2016/01</t>
+  </si>
+  <si>
+    <t>2016/02</t>
+  </si>
+  <si>
+    <t>2016/03</t>
+  </si>
+  <si>
+    <t>2016/04</t>
+  </si>
+  <si>
+    <t>2017/01</t>
+  </si>
+  <si>
+    <t>2017/02</t>
+  </si>
+  <si>
+    <t>2017/03</t>
+  </si>
+  <si>
+    <t>2017/04</t>
+  </si>
+  <si>
+    <t>2018/01</t>
+  </si>
+  <si>
+    <t>2018/02</t>
+  </si>
+  <si>
+    <t>2018/03</t>
+  </si>
+  <si>
+    <t>2018/04</t>
+  </si>
+  <si>
+    <t>2019/01</t>
+  </si>
+  <si>
+    <t>2019/02</t>
+  </si>
+  <si>
+    <t>2019/03</t>
+  </si>
+  <si>
+    <t>2019/04</t>
+  </si>
+  <si>
+    <t>2020/01</t>
+  </si>
+  <si>
+    <t>2020/02</t>
+  </si>
+  <si>
+    <t>2020/03</t>
+  </si>
+  <si>
+    <t>2020/04</t>
+  </si>
+  <si>
+    <t>2021/01</t>
+  </si>
+  <si>
+    <t>2021/02</t>
+  </si>
+  <si>
+    <t>2021/03</t>
+  </si>
+  <si>
+    <t>2021/04</t>
+  </si>
+  <si>
+    <t>2022/01</t>
+  </si>
+  <si>
+    <t>2022/02</t>
+  </si>
+  <si>
+    <t>2022/03</t>
+  </si>
+  <si>
+    <t>2022/04</t>
+  </si>
+  <si>
+    <t>2023/01</t>
+  </si>
+  <si>
+    <t>2023/02</t>
+  </si>
+  <si>
+    <t>2023/03</t>
+  </si>
+  <si>
+    <t>2023/04</t>
+  </si>
+  <si>
+    <t>2024/01</t>
+  </si>
+  <si>
+    <t>2024/02</t>
+  </si>
+  <si>
+    <t>2024/03</t>
+  </si>
+  <si>
+    <t>2024/04</t>
+  </si>
+  <si>
+    <t>2025/01</t>
+  </si>
+  <si>
+    <t>2025/02</t>
+  </si>
+  <si>
+    <t>2025/03</t>
+  </si>
+  <si>
+    <t>2025/04</t>
+  </si>
+  <si>
+    <t>2026/01</t>
+  </si>
+  <si>
+    <t>2026/02</t>
+  </si>
+  <si>
+    <t>1980/01</t>
   </si>
   <si>
     <t>1980/02</t>
@@ -53,555 +602,6 @@
   </si>
   <si>
     <t>1980/04</t>
-  </si>
-  <si>
-    <t>1981/01</t>
-  </si>
-  <si>
-    <t>1981/02</t>
-  </si>
-  <si>
-    <t>1981/03</t>
-  </si>
-  <si>
-    <t>1981/04</t>
-  </si>
-  <si>
-    <t>1982/01</t>
-  </si>
-  <si>
-    <t>1982/02</t>
-  </si>
-  <si>
-    <t>1982/03</t>
-  </si>
-  <si>
-    <t>1982/04</t>
-  </si>
-  <si>
-    <t>1983/01</t>
-  </si>
-  <si>
-    <t>1983/02</t>
-  </si>
-  <si>
-    <t>1983/03</t>
-  </si>
-  <si>
-    <t>1983/04</t>
-  </si>
-  <si>
-    <t>1984/01</t>
-  </si>
-  <si>
-    <t>1984/02</t>
-  </si>
-  <si>
-    <t>1984/03</t>
-  </si>
-  <si>
-    <t>1984/04</t>
-  </si>
-  <si>
-    <t>1985/01</t>
-  </si>
-  <si>
-    <t>1985/02</t>
-  </si>
-  <si>
-    <t>1985/03</t>
-  </si>
-  <si>
-    <t>1985/04</t>
-  </si>
-  <si>
-    <t>1986/01</t>
-  </si>
-  <si>
-    <t>1986/02</t>
-  </si>
-  <si>
-    <t>1986/03</t>
-  </si>
-  <si>
-    <t>1986/04</t>
-  </si>
-  <si>
-    <t>1987/01</t>
-  </si>
-  <si>
-    <t>1987/02</t>
-  </si>
-  <si>
-    <t>1987/03</t>
-  </si>
-  <si>
-    <t>1987/04</t>
-  </si>
-  <si>
-    <t>1988/01</t>
-  </si>
-  <si>
-    <t>1988/02</t>
-  </si>
-  <si>
-    <t>1988/03</t>
-  </si>
-  <si>
-    <t>1988/04</t>
-  </si>
-  <si>
-    <t>1989/01</t>
-  </si>
-  <si>
-    <t>1989/02</t>
-  </si>
-  <si>
-    <t>1989/03</t>
-  </si>
-  <si>
-    <t>1989/04</t>
-  </si>
-  <si>
-    <t>1990/01</t>
-  </si>
-  <si>
-    <t>1990/02</t>
-  </si>
-  <si>
-    <t>1990/03</t>
-  </si>
-  <si>
-    <t>1990/04</t>
-  </si>
-  <si>
-    <t>1991/01</t>
-  </si>
-  <si>
-    <t>1991/02</t>
-  </si>
-  <si>
-    <t>1991/03</t>
-  </si>
-  <si>
-    <t>1991/04</t>
-  </si>
-  <si>
-    <t>1992/01</t>
-  </si>
-  <si>
-    <t>1992/02</t>
-  </si>
-  <si>
-    <t>1992/03</t>
-  </si>
-  <si>
-    <t>1992/04</t>
-  </si>
-  <si>
-    <t>1993/01</t>
-  </si>
-  <si>
-    <t>1993/02</t>
-  </si>
-  <si>
-    <t>1993/03</t>
-  </si>
-  <si>
-    <t>1993/04</t>
-  </si>
-  <si>
-    <t>1994/01</t>
-  </si>
-  <si>
-    <t>1994/02</t>
-  </si>
-  <si>
-    <t>1994/03</t>
-  </si>
-  <si>
-    <t>1994/04</t>
-  </si>
-  <si>
-    <t>1995/01</t>
-  </si>
-  <si>
-    <t>1995/02</t>
-  </si>
-  <si>
-    <t>1995/03</t>
-  </si>
-  <si>
-    <t>1995/04</t>
-  </si>
-  <si>
-    <t>1996/01</t>
-  </si>
-  <si>
-    <t>1996/02</t>
-  </si>
-  <si>
-    <t>1996/03</t>
-  </si>
-  <si>
-    <t>1996/04</t>
-  </si>
-  <si>
-    <t>1997/01</t>
-  </si>
-  <si>
-    <t>1997/02</t>
-  </si>
-  <si>
-    <t>1997/03</t>
-  </si>
-  <si>
-    <t>1997/04</t>
-  </si>
-  <si>
-    <t>1998/01</t>
-  </si>
-  <si>
-    <t>1998/02</t>
-  </si>
-  <si>
-    <t>1998/03</t>
-  </si>
-  <si>
-    <t>1998/04</t>
-  </si>
-  <si>
-    <t>1999/01</t>
-  </si>
-  <si>
-    <t>1999/02</t>
-  </si>
-  <si>
-    <t>1999/03</t>
-  </si>
-  <si>
-    <t>1999/04</t>
-  </si>
-  <si>
-    <t>2000/01</t>
-  </si>
-  <si>
-    <t>2000/02</t>
-  </si>
-  <si>
-    <t>2000/03</t>
-  </si>
-  <si>
-    <t>2000/04</t>
-  </si>
-  <si>
-    <t>2001/01</t>
-  </si>
-  <si>
-    <t>2001/02</t>
-  </si>
-  <si>
-    <t>2001/03</t>
-  </si>
-  <si>
-    <t>2001/04</t>
-  </si>
-  <si>
-    <t>2002/01</t>
-  </si>
-  <si>
-    <t>2002/02</t>
-  </si>
-  <si>
-    <t>2002/03</t>
-  </si>
-  <si>
-    <t>2002/04</t>
-  </si>
-  <si>
-    <t>2003/01</t>
-  </si>
-  <si>
-    <t>2003/02</t>
-  </si>
-  <si>
-    <t>2003/03</t>
-  </si>
-  <si>
-    <t>2003/04</t>
-  </si>
-  <si>
-    <t>2004/01</t>
-  </si>
-  <si>
-    <t>2004/02</t>
-  </si>
-  <si>
-    <t>2004/03</t>
-  </si>
-  <si>
-    <t>2004/04</t>
-  </si>
-  <si>
-    <t>2005/01</t>
-  </si>
-  <si>
-    <t>2005/02</t>
-  </si>
-  <si>
-    <t>2005/03</t>
-  </si>
-  <si>
-    <t>2005/04</t>
-  </si>
-  <si>
-    <t>2006/01</t>
-  </si>
-  <si>
-    <t>2006/02</t>
-  </si>
-  <si>
-    <t>2006/03</t>
-  </si>
-  <si>
-    <t>2006/04</t>
-  </si>
-  <si>
-    <t>2007/01</t>
-  </si>
-  <si>
-    <t>2007/02</t>
-  </si>
-  <si>
-    <t>2007/03</t>
-  </si>
-  <si>
-    <t>2007/04</t>
-  </si>
-  <si>
-    <t>2008/01</t>
-  </si>
-  <si>
-    <t>2008/02</t>
-  </si>
-  <si>
-    <t>2008/03</t>
-  </si>
-  <si>
-    <t>2008/04</t>
-  </si>
-  <si>
-    <t>2009/01</t>
-  </si>
-  <si>
-    <t>2009/02</t>
-  </si>
-  <si>
-    <t>2009/03</t>
-  </si>
-  <si>
-    <t>2009/04</t>
-  </si>
-  <si>
-    <t>2010/01</t>
-  </si>
-  <si>
-    <t>2010/02</t>
-  </si>
-  <si>
-    <t>2010/03</t>
-  </si>
-  <si>
-    <t>2010/04</t>
-  </si>
-  <si>
-    <t>2011/01</t>
-  </si>
-  <si>
-    <t>2011/02</t>
-  </si>
-  <si>
-    <t>2011/03</t>
-  </si>
-  <si>
-    <t>2011/04</t>
-  </si>
-  <si>
-    <t>2012/01</t>
-  </si>
-  <si>
-    <t>2012/02</t>
-  </si>
-  <si>
-    <t>2012/03</t>
-  </si>
-  <si>
-    <t>2012/04</t>
-  </si>
-  <si>
-    <t>2013/01</t>
-  </si>
-  <si>
-    <t>2013/02</t>
-  </si>
-  <si>
-    <t>2013/03</t>
-  </si>
-  <si>
-    <t>2013/04</t>
-  </si>
-  <si>
-    <t>2014/01</t>
-  </si>
-  <si>
-    <t>2014/02</t>
-  </si>
-  <si>
-    <t>2014/03</t>
-  </si>
-  <si>
-    <t>2014/04</t>
-  </si>
-  <si>
-    <t>2015/01</t>
-  </si>
-  <si>
-    <t>2015/02</t>
-  </si>
-  <si>
-    <t>2015/03</t>
-  </si>
-  <si>
-    <t>2015/04</t>
-  </si>
-  <si>
-    <t>2016/01</t>
-  </si>
-  <si>
-    <t>2016/02</t>
-  </si>
-  <si>
-    <t>2016/03</t>
-  </si>
-  <si>
-    <t>2016/04</t>
-  </si>
-  <si>
-    <t>2017/01</t>
-  </si>
-  <si>
-    <t>2017/02</t>
-  </si>
-  <si>
-    <t>2017/03</t>
-  </si>
-  <si>
-    <t>2017/04</t>
-  </si>
-  <si>
-    <t>2018/01</t>
-  </si>
-  <si>
-    <t>2018/02</t>
-  </si>
-  <si>
-    <t>2018/03</t>
-  </si>
-  <si>
-    <t>2018/04</t>
-  </si>
-  <si>
-    <t>2019/01</t>
-  </si>
-  <si>
-    <t>2019/02</t>
-  </si>
-  <si>
-    <t>2019/03</t>
-  </si>
-  <si>
-    <t>2019/04</t>
-  </si>
-  <si>
-    <t>2020/01</t>
-  </si>
-  <si>
-    <t>2020/02</t>
-  </si>
-  <si>
-    <t>2020/03</t>
-  </si>
-  <si>
-    <t>2020/04</t>
-  </si>
-  <si>
-    <t>2021/01</t>
-  </si>
-  <si>
-    <t>2021/02</t>
-  </si>
-  <si>
-    <t>2021/03</t>
-  </si>
-  <si>
-    <t>2021/04</t>
-  </si>
-  <si>
-    <t>2022/01</t>
-  </si>
-  <si>
-    <t>2022/02</t>
-  </si>
-  <si>
-    <t>2022/03</t>
-  </si>
-  <si>
-    <t>2022/04</t>
-  </si>
-  <si>
-    <t>2023/01</t>
-  </si>
-  <si>
-    <t>2023/02</t>
-  </si>
-  <si>
-    <t>2023/03</t>
-  </si>
-  <si>
-    <t>2023/04</t>
-  </si>
-  <si>
-    <t>2024/01</t>
-  </si>
-  <si>
-    <t>2024/02</t>
-  </si>
-  <si>
-    <t>2024/03</t>
-  </si>
-  <si>
-    <t>2024/04</t>
-  </si>
-  <si>
-    <t>2025/01</t>
-  </si>
-  <si>
-    <t>2025/02</t>
-  </si>
-  <si>
-    <t>2025/03</t>
-  </si>
-  <si>
-    <t>2025/04</t>
-  </si>
-  <si>
-    <t>2026/01</t>
-  </si>
-  <si>
-    <t>2026/02</t>
-  </si>
-  <si>
-    <t>1980/01</t>
   </si>
 </sst>
 </file>
@@ -961,7 +961,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>0.283766252154</v>
+        <v>9.124655050428</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -975,7 +975,7 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>2.33595572864</v>
+        <v>11.805371957054</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -989,7 +989,7 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>3.132028567217</v>
+        <v>9.882178857568</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1003,7 +1003,7 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>3.102794806827</v>
+        <v>7.692580211146</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1017,7 +1017,7 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>2.747301074124</v>
+        <v>3.446230516873</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1031,7 +1031,7 @@
         <v>15</v>
       </c>
       <c r="D7">
-        <v>0.5756485051</v>
+        <v>0.766722200299</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1045,7 +1045,7 @@
         <v>16</v>
       </c>
       <c r="D8">
-        <v>1.076938720062</v>
+        <v>-0.377540987278</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1059,7 +1059,7 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>-0.962578316821</v>
+        <v>-3.821404256915</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1073,7 +1073,7 @@
         <v>18</v>
       </c>
       <c r="D10">
-        <v>0.085896725624</v>
+        <v>-4.616339161488</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1087,7 +1087,7 @@
         <v>19</v>
       </c>
       <c r="D11">
-        <v>-0.566444932477</v>
+        <v>-6.417466526699</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1101,7 +1101,7 @@
         <v>20</v>
       </c>
       <c r="D12">
-        <v>-2.417204670044</v>
+        <v>-5.537452155845</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1115,7 +1115,7 @@
         <v>21</v>
       </c>
       <c r="D13">
-        <v>-1.781141976922</v>
+        <v>-1.894830695466</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1129,7 +1129,7 @@
         <v>22</v>
       </c>
       <c r="D14">
-        <v>-1.80402284634</v>
+        <v>2.662643804</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1143,7 +1143,7 @@
         <v>23</v>
       </c>
       <c r="D15">
-        <v>0.368590208771</v>
+        <v>3.283930394359</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1157,7 +1157,7 @@
         <v>24</v>
       </c>
       <c r="D16">
-        <v>1.345738343298</v>
+        <v>4.813443306655</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1171,7 +1171,7 @@
         <v>25</v>
       </c>
       <c r="D17">
-        <v>2.781613930643</v>
+        <v>3.278109649897</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1185,7 +1185,7 @@
         <v>26</v>
       </c>
       <c r="D18">
-        <v>-1.209767316069</v>
+        <v>2.078440627669</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1199,7 +1199,7 @@
         <v>27</v>
       </c>
       <c r="D19">
-        <v>1.85493037928</v>
+        <v>2.748721369946</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1213,7 +1213,7 @@
         <v>28</v>
       </c>
       <c r="D20">
-        <v>-0.138799499735</v>
+        <v>1.39004165901</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1227,7 +1227,7 @@
         <v>29</v>
       </c>
       <c r="D21">
-        <v>1.587712157022</v>
+        <v>1.32190934133</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1241,7 +1241,7 @@
         <v>30</v>
       </c>
       <c r="D22">
-        <v>-0.56107803275</v>
+        <v>-2.294376883874</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1255,7 +1255,7 @@
         <v>31</v>
       </c>
       <c r="D23">
-        <v>0.508069556877</v>
+        <v>-2.967118079402</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1269,7 +1269,7 @@
         <v>32</v>
       </c>
       <c r="D24">
-        <v>-0.205904463152</v>
+        <v>-5.00705031576</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1283,7 +1283,7 @@
         <v>33</v>
       </c>
       <c r="D25">
-        <v>-2.03806085211</v>
+        <v>-5.433350936695</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1297,7 +1297,7 @@
         <v>34</v>
       </c>
       <c r="D26">
-        <v>-1.24575366464</v>
+        <v>-2.489819946123</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1311,7 +1311,7 @@
         <v>35</v>
       </c>
       <c r="D27">
-        <v>-1.604921905862</v>
+        <v>1.478718639899</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1325,7 +1325,7 @@
         <v>36</v>
       </c>
       <c r="D28">
-        <v>-0.653751224775</v>
+        <v>3.971935877303</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1339,7 +1339,7 @@
         <v>37</v>
       </c>
       <c r="D29">
-        <v>1.011153713856</v>
+        <v>5.551494692051</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1353,7 +1353,7 @@
         <v>38</v>
       </c>
       <c r="D30">
-        <v>2.773416814779</v>
+        <v>3.776306738187</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1367,7 +1367,7 @@
         <v>39</v>
       </c>
       <c r="D31">
-        <v>0.812533774187</v>
+        <v>0.642337023222</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1381,7 +1381,7 @@
         <v>40</v>
       </c>
       <c r="D32">
-        <v>0.855533387856</v>
+        <v>-0.06715422227999999</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1395,7 +1395,7 @@
         <v>41</v>
       </c>
       <c r="D33">
-        <v>-0.68767379969</v>
+        <v>0.603268511656</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1409,7 +1409,7 @@
         <v>42</v>
       </c>
       <c r="D34">
-        <v>-0.330266346865</v>
+        <v>3.199951010793</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1423,7 +1423,7 @@
         <v>43</v>
       </c>
       <c r="D35">
-        <v>0.101842704551</v>
+        <v>3.408553037236</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1437,7 +1437,7 @@
         <v>44</v>
       </c>
       <c r="D36">
-        <v>1.532146186182</v>
+        <v>5.261597054324</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1451,7 +1451,7 @@
         <v>45</v>
       </c>
       <c r="D37">
-        <v>1.875688039425</v>
+        <v>2.563121576501</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1465,7 +1465,7 @@
         <v>46</v>
       </c>
       <c r="D38">
-        <v>-0.128800084416</v>
+        <v>3.289535726012</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1479,7 +1479,7 @@
         <v>47</v>
       </c>
       <c r="D39">
-        <v>1.895631663733</v>
+        <v>5.462403169658</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1493,7 +1493,7 @@
         <v>48</v>
       </c>
       <c r="D40">
-        <v>-1.070721472692</v>
+        <v>5.051260840014</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1507,7 +1507,7 @@
         <v>49</v>
       </c>
       <c r="D41">
-        <v>2.597233368248</v>
+        <v>7.21255531764</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1521,7 +1521,7 @@
         <v>50</v>
       </c>
       <c r="D42">
-        <v>1.972156971196</v>
+        <v>4.946461751422</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1535,7 +1535,7 @@
         <v>51</v>
       </c>
       <c r="D43">
-        <v>1.498394296446</v>
+        <v>4.041049938286</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1549,7 +1549,7 @@
         <v>52</v>
       </c>
       <c r="D44">
-        <v>0.96462109861</v>
+        <v>3.026419061992</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1563,7 +1563,7 @@
         <v>53</v>
       </c>
       <c r="D45">
-        <v>0.428691355992</v>
+        <v>3.863362970228</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1577,7 +1577,7 @@
         <v>54</v>
       </c>
       <c r="D46">
-        <v>1.092405581851</v>
+        <v>3.387115538055</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1591,7 +1591,7 @@
         <v>55</v>
       </c>
       <c r="D47">
-        <v>0.5085599492490001</v>
+        <v>3.68084046514</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1605,7 +1605,7 @@
         <v>56</v>
       </c>
       <c r="D48">
-        <v>1.784815815121</v>
+        <v>4.63943634059</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1619,7 +1619,7 @@
         <v>57</v>
       </c>
       <c r="D49">
-        <v>-0.031806985357</v>
+        <v>2.774162958262</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1633,7 +1633,7 @@
         <v>58</v>
       </c>
       <c r="D50">
-        <v>1.379611190633</v>
+        <v>3.925600199098</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1647,7 +1647,7 @@
         <v>59</v>
       </c>
       <c r="D51">
-        <v>1.437826056493</v>
+        <v>2.545887318465</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1661,7 +1661,7 @@
         <v>60</v>
       </c>
       <c r="D52">
-        <v>-0.029571898582</v>
+        <v>2.268452635295</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1675,7 +1675,7 @@
         <v>61</v>
       </c>
       <c r="D53">
-        <v>1.088193382663</v>
+        <v>2.940234373012</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1689,7 +1689,7 @@
         <v>62</v>
       </c>
       <c r="D54">
-        <v>-0.00641254642089333</v>
+        <v>2.82178973071234</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1703,7 +1703,7 @@
         <v>63</v>
       </c>
       <c r="D55">
-        <v>1.16143418740577</v>
+        <v>5.17205342293405</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1717,7 +1717,7 @@
         <v>64</v>
       </c>
       <c r="D56">
-        <v>0.629061485468034</v>
+        <v>4.52696119297973</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1731,7 +1731,7 @@
         <v>65</v>
       </c>
       <c r="D57">
-        <v>1.01238123242125</v>
+        <v>4.99090863730258</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1745,7 +1745,7 @@
         <v>66</v>
       </c>
       <c r="D58">
-        <v>2.27920510974548</v>
+        <v>-0.79323065804966</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1759,7 +1759,7 @@
         <v>67</v>
       </c>
       <c r="D59">
-        <v>0.540941831866189</v>
+        <v>-8.90602026709497</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1773,7 +1773,7 @@
         <v>68</v>
       </c>
       <c r="D60">
-        <v>1.07570793312087</v>
+        <v>-7.45183804761752</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1787,7 +1787,7 @@
         <v>69</v>
       </c>
       <c r="D61">
-        <v>-4.55257378308341</v>
+        <v>-6.34352251849618</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1801,7 +1801,7 @@
         <v>70</v>
       </c>
       <c r="D62">
-        <v>-6.08483776696255</v>
+        <v>0.384268140325819</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1815,7 +1815,7 @@
         <v>71</v>
       </c>
       <c r="D63">
-        <v>2.14593099108506</v>
+        <v>8.05085883546743</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1829,7 +1829,7 @@
         <v>72</v>
       </c>
       <c r="D64">
-        <v>2.28614555128609</v>
+        <v>7.35350244267947</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1843,7 +1843,7 @@
         <v>73</v>
       </c>
       <c r="D65">
-        <v>2.303869249782</v>
+        <v>8.280136301370581</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1857,7 +1857,7 @@
         <v>74</v>
       </c>
       <c r="D66">
-        <v>1.08769157699828</v>
+        <v>6.20806380282288</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1871,7 +1871,7 @@
         <v>75</v>
       </c>
       <c r="D67">
-        <v>1.48668479219665</v>
+        <v>7.58361466665123</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1885,7 +1885,7 @@
         <v>76</v>
       </c>
       <c r="D68">
-        <v>3.16903994770726</v>
+        <v>8.18946940237784</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1899,7 +1899,7 @@
         <v>77</v>
       </c>
       <c r="D69">
-        <v>0.346159911686068</v>
+        <v>7.82390615805519</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1913,7 +1913,7 @@
         <v>78</v>
       </c>
       <c r="D70">
-        <v>2.39692607852639</v>
+        <v>9.130385130168699</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1927,7 +1927,7 @@
         <v>79</v>
       </c>
       <c r="D71">
-        <v>2.05820480279549</v>
+        <v>7.30511732023689</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1941,7 +1941,7 @@
         <v>80</v>
       </c>
       <c r="D72">
-        <v>2.82044031813825</v>
+        <v>5.66962923784408</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1955,7 +1955,7 @@
         <v>81</v>
       </c>
       <c r="D73">
-        <v>1.56203264833857</v>
+        <v>2.95526871889429</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1969,7 +1969,7 @@
         <v>82</v>
       </c>
       <c r="D74">
-        <v>0.684279204017809</v>
+        <v>2.28134278006308</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1983,7 +1983,7 @@
         <v>83</v>
       </c>
       <c r="D75">
-        <v>0.502687397532852</v>
+        <v>2.31184196416569</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1997,7 +1997,7 @@
         <v>84</v>
       </c>
       <c r="D76">
-        <v>0.179267582380844</v>
+        <v>2.76026205302955</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2011,7 +2011,7 @@
         <v>85</v>
       </c>
       <c r="D77">
-        <v>0.897226572322992</v>
+        <v>3.60307738543223</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2025,7 +2025,7 @@
         <v>86</v>
       </c>
       <c r="D78">
-        <v>0.714302161130186</v>
+        <v>4.77449013439415</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2039,7 +2039,7 @@
         <v>87</v>
       </c>
       <c r="D79">
-        <v>0.943178186757844</v>
+        <v>5.38361125971189</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2053,7 +2053,7 @@
         <v>88</v>
       </c>
       <c r="D80">
-        <v>1.0009142093983</v>
+        <v>5.54103197518632</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2067,7 +2067,7 @@
         <v>89</v>
       </c>
       <c r="D81">
-        <v>2.03804497776485</v>
+        <v>3.31780623938527</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2081,7 +2081,7 @@
         <v>90</v>
       </c>
       <c r="D82">
-        <v>1.29981881684751</v>
+        <v>1.93372618334094</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2095,7 +2095,7 @@
         <v>91</v>
       </c>
       <c r="D83">
-        <v>1.09396583905476</v>
+        <v>-0.16026581711307</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2109,7 +2109,7 @@
         <v>92</v>
       </c>
       <c r="D84">
-        <v>-1.12667377801651</v>
+        <v>-1.43962269408871</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2123,7 +2123,7 @@
         <v>93</v>
       </c>
       <c r="D85">
-        <v>0.671109033690955</v>
+        <v>-1.17844704105756</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2137,7 +2137,7 @@
         <v>94</v>
       </c>
       <c r="D86">
-        <v>-0.781151026915413</v>
+        <v>-2.45068446167212</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2151,7 +2151,7 @@
         <v>95</v>
       </c>
       <c r="D87">
-        <v>-0.201462894559638</v>
+        <v>-0.598660046362403</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2165,7 +2165,7 @@
         <v>96</v>
       </c>
       <c r="D88">
-        <v>-0.864668840035819</v>
+        <v>0.51581591724719</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2179,7 +2179,7 @@
         <v>97</v>
       </c>
       <c r="D89">
-        <v>-0.624939735555183</v>
+        <v>1.60705827097298</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2193,7 +2193,7 @@
         <v>98</v>
       </c>
       <c r="D90">
-        <v>1.10257034768389</v>
+        <v>2.23279440436086</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2207,7 +2207,7 @@
         <v>99</v>
       </c>
       <c r="D91">
-        <v>0.917466396124869</v>
+        <v>1.2222144902893</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2221,7 +2221,7 @@
         <v>100</v>
       </c>
       <c r="D92">
-        <v>0.21158638532541</v>
+        <v>0.360536830608692</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2235,7 +2235,7 @@
         <v>101</v>
       </c>
       <c r="D93">
-        <v>-0.0129491216823856</v>
+        <v>1.05373435141878</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2249,7 +2249,7 @@
         <v>102</v>
       </c>
       <c r="D94">
-        <v>0.103162795052042</v>
+        <v>2.37903473569607</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2263,7 +2263,7 @@
         <v>103</v>
       </c>
       <c r="D95">
-        <v>0.0583829755240336</v>
+        <v>3.65219181426818</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2277,7 +2277,7 @@
         <v>104</v>
       </c>
       <c r="D96">
-        <v>0.903755094586115</v>
+        <v>3.53889466794848</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2291,7 +2291,7 @@
         <v>105</v>
       </c>
       <c r="D97">
-        <v>1.29836191300899</v>
+        <v>3.70356751504026</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2305,7 +2305,7 @@
         <v>106</v>
       </c>
       <c r="D98">
-        <v>1.34801776588662</v>
+        <v>2.60067983826201</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2319,7 +2319,7 @@
         <v>107</v>
       </c>
       <c r="D99">
-        <v>-0.0509859539512238</v>
+        <v>1.2707471104889</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2333,7 +2333,7 @@
         <v>108</v>
       </c>
       <c r="D100">
-        <v>1.06423689890676</v>
+        <v>2.33881957144219</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2347,7 +2347,7 @@
         <v>109</v>
       </c>
       <c r="D101">
-        <v>0.221053603287841</v>
+        <v>3.13679633638488</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2361,7 +2361,7 @@
         <v>110</v>
       </c>
       <c r="D102">
-        <v>0.0343223212340342</v>
+        <v>4.96450995950648</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2375,7 +2375,7 @@
         <v>111</v>
       </c>
       <c r="D103">
-        <v>1.00314658133607</v>
+        <v>5.79064684392698</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2389,7 +2389,7 @@
         <v>112</v>
       </c>
       <c r="D104">
-        <v>1.85227523225583</v>
+        <v>5.0069853019614</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2403,7 +2403,7 @@
         <v>113</v>
       </c>
       <c r="D105">
-        <v>1.99709660152967</v>
+        <v>3.4734293101135</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2417,7 +2417,7 @@
         <v>114</v>
       </c>
       <c r="D106">
-        <v>0.8216555199453059</v>
+        <v>2.1911511188615</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2431,7 +2431,7 @@
         <v>115</v>
       </c>
       <c r="D107">
-        <v>0.254949231620664</v>
+        <v>1.98094374606039</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2445,7 +2445,7 @@
         <v>116</v>
       </c>
       <c r="D108">
-        <v>0.364791647077151</v>
+        <v>2.08638509222026</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2459,7 +2459,7 @@
         <v>117</v>
       </c>
       <c r="D109">
-        <v>0.733113631068847</v>
+        <v>1.98244766529379</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2473,7 +2473,7 @@
         <v>118</v>
       </c>
       <c r="D110">
-        <v>0.614265201935723</v>
+        <v>1.17662646739099</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2487,7 +2487,7 @@
         <v>119</v>
       </c>
       <c r="D111">
-        <v>0.358606017073577</v>
+        <v>1.35306347127755</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2501,7 +2501,7 @@
         <v>120</v>
       </c>
       <c r="D112">
-        <v>0.262607029722108</v>
+        <v>1.05309784689729</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2515,7 +2515,7 @@
         <v>121</v>
       </c>
       <c r="D113">
-        <v>-0.06283586958518519</v>
+        <v>-0.790533290813328</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2529,7 +2529,7 @@
         <v>122</v>
       </c>
       <c r="D114">
-        <v>0.789721531330129</v>
+        <v>-6.83668409737537</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2543,7 +2543,7 @@
         <v>123</v>
       </c>
       <c r="D115">
-        <v>0.0615835997455106</v>
+        <v>-9.15077381943412</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2557,7 +2557,7 @@
         <v>124</v>
       </c>
       <c r="D116">
-        <v>-1.56660224942435</v>
+        <v>-5.9041180355529</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2571,7 +2571,7 @@
         <v>125</v>
       </c>
       <c r="D117">
-        <v>-6.15333494749908</v>
+        <v>-2.30979409261153</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2585,7 +2585,7 @@
         <v>126</v>
       </c>
       <c r="D118">
-        <v>-1.71380098099217</v>
+        <v>4.54763778051975</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2599,7 +2599,7 @@
         <v>127</v>
       </c>
       <c r="D119">
-        <v>3.63745906722332</v>
+        <v>7.48990914911801</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2613,7 +2613,7 @@
         <v>128</v>
       </c>
       <c r="D120">
-        <v>2.19340840070851</v>
+        <v>4.71371503270891</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2627,7 +2627,7 @@
         <v>129</v>
       </c>
       <c r="D121">
-        <v>0.434296905055165</v>
+        <v>3.31857820009092</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2641,7 +2641,7 @@
         <v>130</v>
       </c>
       <c r="D122">
-        <v>1.05225548323011</v>
+        <v>3.60742656102238</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2655,7 +2655,7 @@
         <v>131</v>
       </c>
       <c r="D123">
-        <v>0.960764051109098</v>
+        <v>2.80151316822362</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2669,7 +2669,7 @@
         <v>132</v>
       </c>
       <c r="D124">
-        <v>0.8318504799904149</v>
+        <v>3.75173816701016</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2683,7 +2683,7 @@
         <v>133</v>
       </c>
       <c r="D125">
-        <v>0.715081663689232</v>
+        <v>3.64143090194049</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2697,7 +2697,7 @@
         <v>134</v>
       </c>
       <c r="D126">
-        <v>0.266217563269899</v>
+        <v>3.86599371924852</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2711,7 +2711,7 @@
         <v>135</v>
       </c>
       <c r="D127">
-        <v>1.89397445766184</v>
+        <v>4.22923821814714</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2725,7 +2725,7 @@
         <v>136</v>
       </c>
       <c r="D128">
-        <v>0.724647594960603</v>
+        <v>2.57446993508279</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2739,7 +2739,7 @@
         <v>137</v>
       </c>
       <c r="D129">
-        <v>0.933303877402247</v>
+        <v>2.62813644470874</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2753,7 +2753,7 @@
         <v>138</v>
       </c>
       <c r="D130">
-        <v>0.616872774384314</v>
+        <v>1.76544737576225</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2767,7 +2767,7 @@
         <v>139</v>
       </c>
       <c r="D131">
-        <v>0.276281379880605</v>
+        <v>0.734092112939644</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2781,7 +2781,7 @@
         <v>140</v>
       </c>
       <c r="D132">
-        <v>0.77734628570838</v>
+        <v>1.08422140469493</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2795,7 +2795,7 @@
         <v>141</v>
       </c>
       <c r="D133">
-        <v>0.08486152071383039</v>
+        <v>0.79716261909978</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2809,7 +2809,7 @@
         <v>142</v>
       </c>
       <c r="D134">
-        <v>-0.402842108619583</v>
+        <v>1.38777414908504</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2823,7 +2823,7 @@
         <v>143</v>
       </c>
       <c r="D135">
-        <v>0.6248194233865469</v>
+        <v>3.07264160296593</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2837,7 +2837,7 @@
         <v>144</v>
       </c>
       <c r="D136">
-        <v>0.491158963510396</v>
+        <v>2.61374383912148</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2851,7 +2851,7 @@
         <v>145</v>
       </c>
       <c r="D137">
-        <v>0.67129938915349</v>
+        <v>2.97902951468255</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2865,7 +2865,7 @@
         <v>146</v>
       </c>
       <c r="D138">
-        <v>1.25226878851354</v>
+        <v>2.8043517721958</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2879,7 +2879,7 @@
         <v>147</v>
       </c>
       <c r="D139">
-        <v>0.176819799989736</v>
+        <v>2.40274834784488</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2893,7 +2893,7 @@
         <v>148</v>
       </c>
       <c r="D140">
-        <v>0.8488886351560641</v>
+        <v>3.43342950498592</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2907,7 +2907,7 @@
         <v>149</v>
       </c>
       <c r="D141">
-        <v>0.500536124114204</v>
+        <v>2.25841123276102</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2921,7 +2921,7 @@
         <v>150</v>
       </c>
       <c r="D142">
-        <v>0.85672854952763</v>
+        <v>1.60074321781179</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2935,7 +2935,7 @@
         <v>151</v>
       </c>
       <c r="D143">
-        <v>1.18509704074736</v>
+        <v>1.23209011957058</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2949,7 +2949,7 @@
         <v>152</v>
       </c>
       <c r="D144">
-        <v>-0.296768890143062</v>
+        <v>0.914896692320867</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2963,7 +2963,7 @@
         <v>153</v>
       </c>
       <c r="D145">
-        <v>-0.145826236666369</v>
+        <v>2.34308418716372</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2977,7 +2977,7 @@
         <v>154</v>
       </c>
       <c r="D146">
-        <v>0.490775070441862</v>
+        <v>3.10494748579455</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2991,7 +2991,7 @@
         <v>155</v>
       </c>
       <c r="D147">
-        <v>0.868050858266689</v>
+        <v>2.69127195680336</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3005,7 +3005,7 @@
         <v>156</v>
       </c>
       <c r="D148">
-        <v>1.11427063458311</v>
+        <v>1.21540031757053</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3019,7 +3019,7 @@
         <v>157</v>
       </c>
       <c r="D149">
-        <v>0.597509092824611</v>
+        <v>1.49405913504092</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3033,7 +3033,7 @@
         <v>158</v>
       </c>
       <c r="D150">
-        <v>0.0875880697237319</v>
+        <v>2.15199522354916</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3047,7 +3047,7 @@
         <v>159</v>
       </c>
       <c r="D151">
-        <v>-0.581617577323745</v>
+        <v>1.76149662564593</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3061,7 +3061,7 @@
         <v>160</v>
       </c>
       <c r="D152">
-        <v>1.3926510292267</v>
+        <v>2.76841142174641</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3075,7 +3075,7 @@
         <v>161</v>
       </c>
       <c r="D153">
-        <v>1.24963328817425</v>
+        <v>1.1632916142895</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3089,7 +3089,7 @@
         <v>162</v>
       </c>
       <c r="D154">
-        <v>-0.295018875184316</v>
+        <v>-0.0597420902482826</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3103,7 +3103,7 @@
         <v>163</v>
       </c>
       <c r="D155">
-        <v>0.402112454026238</v>
+        <v>-0.06804254524888349</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3117,7 +3117,7 @@
         <v>164</v>
       </c>
       <c r="D156">
-        <v>-0.190981044540461</v>
+        <v>-0.438725353203986</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3131,7 +3131,7 @@
         <v>165</v>
       </c>
       <c r="D157">
-        <v>0.0255557388229688</v>
+        <v>-0.990298968647934</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3145,7 +3145,7 @@
         <v>166</v>
       </c>
       <c r="D158">
-        <v>-0.303299789467226</v>
+        <v>-2.21915580376183</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3159,7 +3159,7 @@
         <v>167</v>
       </c>
       <c r="D159">
-        <v>0.0296856756762276</v>
+        <v>-20.4706531046103</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3173,7 +3173,7 @@
         <v>168</v>
       </c>
       <c r="D160">
-        <v>-0.743927173790804</v>
+        <v>-8.114518275349379</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3187,7 +3187,7 @@
         <v>169</v>
       </c>
       <c r="D161">
-        <v>-1.21590935576202</v>
+        <v>-3.44681318996457</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3201,7 +3201,7 @@
         <v>170</v>
       </c>
       <c r="D162">
-        <v>-18.9124053842627</v>
+        <v>-1.52021122601162</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3215,7 +3215,7 @@
         <v>171</v>
       </c>
       <c r="D163">
-        <v>15.5708705512797</v>
+        <v>22.5198903326093</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3229,7 +3229,7 @@
         <v>172</v>
       </c>
       <c r="D164">
-        <v>4.29819773201932</v>
+        <v>5.10235700045289</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3243,7 +3243,7 @@
         <v>173</v>
       </c>
       <c r="D165">
-        <v>0.75520759366543</v>
+        <v>1.94868830643919</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3257,7 +3257,7 @@
         <v>174</v>
       </c>
       <c r="D166">
-        <v>0.882052280348922</v>
+        <v>2.64624871085353</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3271,7 +3271,7 @@
         <v>175</v>
       </c>
       <c r="D167">
-        <v>-0.858784132450396</v>
+        <v>2.90804674355962</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3285,7 +3285,7 @@
         <v>176</v>
       </c>
       <c r="D168">
-        <v>1.16865839135445</v>
+        <v>4.60008757551484</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3299,7 +3299,7 @@
         <v>177</v>
       </c>
       <c r="D169">
-        <v>1.44460188135485</v>
+        <v>4.67400505541721</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3313,7 +3313,7 @@
         <v>178</v>
       </c>
       <c r="D170">
-        <v>1.13935075110692</v>
+        <v>3.77179397115653</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3327,7 +3327,7 @@
         <v>179</v>
       </c>
       <c r="D171">
-        <v>0.771321487915766</v>
+        <v>3.35357333870012</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3341,7 +3341,7 @@
         <v>180</v>
       </c>
       <c r="D172">
-        <v>1.24015099185533</v>
+        <v>3.21223901248618</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3355,7 +3355,7 @@
         <v>181</v>
       </c>
       <c r="D173">
-        <v>0.570225820103398</v>
+        <v>2.13921571997775</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3369,7 +3369,7 @@
         <v>182</v>
       </c>
       <c r="D174">
-        <v>0.731739379859775</v>
+        <v>1.97982146977274</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3383,7 +3383,7 @@
         <v>183</v>
       </c>
       <c r="D175">
-        <v>0.633518349000473</v>
+        <v>1.07992915834643</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3397,7 +3397,7 @@
         <v>184</v>
       </c>
       <c r="D176">
-        <v>0.187630077759193</v>
+        <v>1.4335903209204</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3411,7 +3411,7 @@
         <v>185</v>
       </c>
       <c r="D177">
-        <v>0.41328007086745</v>
+        <v>0.352984350732571</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3425,7 +3425,7 @@
         <v>186</v>
       </c>
       <c r="D178">
-        <v>-0.157139581468879</v>
+        <v>0.713955793035045</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3439,7 +3439,7 @@
         <v>187</v>
       </c>
       <c r="D179">
-        <v>0.985617597481969</v>
+        <v>0.848255135504099</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3453,7 +3453,7 @@
         <v>188</v>
       </c>
       <c r="D180">
-        <v>-0.87970226114813</v>
+        <v>-0.240685690253069</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3467,7 +3467,7 @@
         <v>189</v>
       </c>
       <c r="D181">
-        <v>0.774468397931272</v>
+        <v>1.59606943658511</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3481,7 +3481,7 @@
         <v>190</v>
       </c>
       <c r="D182">
-        <v>-0.0240018211768223</v>
+        <v>0.469878458114494</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3495,49 +3495,49 @@
         <v>191</v>
       </c>
       <c r="D183">
-        <v>-0.104806442759908</v>
+        <v>1.92544131907043</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B184" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C184" t="s">
         <v>192</v>
       </c>
       <c r="D184">
-        <v>0.945287378218063</v>
+        <v>10290879.5792174</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B185" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C185" t="s">
         <v>193</v>
       </c>
       <c r="D185">
-        <v>-0.342615144761904</v>
+        <v>10320081.622513</v>
       </c>
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B186" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C186" t="s">
         <v>194</v>
       </c>
       <c r="D186">
-        <v>1.42440592221227</v>
+        <v>10561154.1603744</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3548,10 +3548,10 @@
         <v>8</v>
       </c>
       <c r="C187" t="s">
-        <v>13</v>
+        <v>195</v>
       </c>
       <c r="D187">
-        <v>9.124655050428</v>
+        <v>10891932.5257052</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3562,10 +3562,10 @@
         <v>8</v>
       </c>
       <c r="C188" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D188">
-        <v>11.805371957054</v>
+        <v>11229886.8424759</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3576,10 +3576,10 @@
         <v>8</v>
       </c>
       <c r="C189" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D189">
-        <v>9.882178857568</v>
+        <v>11538405.6443222</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3590,10 +3590,10 @@
         <v>8</v>
       </c>
       <c r="C190" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D190">
-        <v>7.692580211146</v>
+        <v>11604826.3039261</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3604,10 +3604,10 @@
         <v>8</v>
       </c>
       <c r="C191" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D191">
-        <v>3.446230516873</v>
+        <v>11729803.171789</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3618,10 +3618,10 @@
         <v>8</v>
       </c>
       <c r="C192" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D192">
-        <v>0.766722200299</v>
+        <v>11616894.6298516</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3632,10 +3632,10 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D193">
-        <v>-0.377540987278</v>
+        <v>11626873.1619578</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3646,10 +3646,10 @@
         <v>8</v>
       </c>
       <c r="C194" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D194">
-        <v>-3.821404256915</v>
+        <v>11561013.3281264</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3660,10 +3660,10 @@
         <v>8</v>
       </c>
       <c r="C195" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D195">
-        <v>-4.616339161488</v>
+        <v>11281559.9740545</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3674,10 +3674,10 @@
         <v>8</v>
       </c>
       <c r="C196" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D196">
-        <v>-6.417466526699</v>
+        <v>11080619.373705</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3688,10 +3688,10 @@
         <v>8</v>
       </c>
       <c r="C197" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D197">
-        <v>-5.537452155845</v>
+        <v>10880722.4686874</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3702,10 +3702,10 @@
         <v>8</v>
       </c>
       <c r="C198" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D198">
-        <v>-1.894830695466</v>
+        <v>10920827.7463505</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3716,10 +3716,10 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D199">
-        <v>2.662643804</v>
+        <v>11067793.5127387</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3730,10 +3730,10 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D200">
-        <v>3.283930394359</v>
+        <v>11375656.7989038</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3744,10 +3744,10 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D201">
-        <v>4.813443306655</v>
+        <v>11238037.8209625</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3758,10 +3758,10 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D202">
-        <v>3.278109649897</v>
+        <v>11446495.5985385</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3772,10 +3772,10 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D203">
-        <v>2.078440627669</v>
+        <v>11430607.9199105</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3786,10 +3786,10 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D204">
-        <v>2.748721369946</v>
+        <v>11612093.0714764</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3800,10 +3800,10 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D205">
-        <v>1.39004165901</v>
+        <v>11546940.1681099</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3814,10 +3814,10 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D206">
-        <v>1.32190934133</v>
+        <v>11605606.6558549</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3828,10 +3828,10 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D207">
-        <v>-2.294376883874</v>
+        <v>11581710.1937746</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3842,10 +3842,10 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D208">
-        <v>-2.967118079402</v>
+        <v>11345667.8923105</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3856,10 +3856,10 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D209">
-        <v>-5.00705031576</v>
+        <v>11204328.8187642</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3870,10 +3870,10 @@
         <v>8</v>
       </c>
       <c r="C210" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D210">
-        <v>-5.433350936695</v>
+        <v>11024508.0911471</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3884,10 +3884,10 @@
         <v>8</v>
       </c>
       <c r="C211" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D211">
-        <v>-2.489819946123</v>
+        <v>10952435.2344758</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3898,10 +3898,10 @@
         <v>8</v>
       </c>
       <c r="C212" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D212">
-        <v>1.478718639899</v>
+        <v>11063181.1901069</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3912,10 +3912,10 @@
         <v>8</v>
       </c>
       <c r="C213" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D213">
-        <v>3.971935877303</v>
+        <v>11370009.3174828</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3926,10 +3926,10 @@
         <v>8</v>
       </c>
       <c r="C214" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D214">
-        <v>5.551494692051</v>
+        <v>11462394.4833155</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3940,10 +3940,10 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D215">
-        <v>3.776306738187</v>
+        <v>11560459.095168</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3954,10 +3954,10 @@
         <v>8</v>
       </c>
       <c r="C216" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D216">
-        <v>0.642337023222</v>
+        <v>11480960.8468467</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3968,10 +3968,10 @@
         <v>8</v>
       </c>
       <c r="C217" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D217">
-        <v>-0.06715422227999999</v>
+        <v>11443043.0968728</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3982,10 +3982,10 @@
         <v>8</v>
       </c>
       <c r="C218" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D218">
-        <v>0.603268511656</v>
+        <v>11454697.0014456</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3996,10 +3996,10 @@
         <v>8</v>
       </c>
       <c r="C219" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D219">
-        <v>3.199951010793</v>
+        <v>11630199.704692</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4010,10 +4010,10 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D220">
-        <v>3.408553037236</v>
+        <v>11848345.9695141</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4024,10 +4024,10 @@
         <v>8</v>
       </c>
       <c r="C221" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D221">
-        <v>5.261597054324</v>
+        <v>11833085.2899035</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4038,10 +4038,10 @@
         <v>8</v>
       </c>
       <c r="C222" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D222">
-        <v>2.563121576501</v>
+        <v>12057397.0014554</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4052,10 +4052,10 @@
         <v>8</v>
       </c>
       <c r="C223" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D223">
-        <v>3.289535726012</v>
+        <v>11928295.8627131</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4066,10 +4066,10 @@
         <v>8</v>
       </c>
       <c r="C224" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D224">
-        <v>5.462403169658</v>
+        <v>12238101.5431228</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4080,10 +4080,10 @@
         <v>8</v>
       </c>
       <c r="C225" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D225">
-        <v>5.051260840014</v>
+        <v>12479456.1158475</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4094,10 +4094,10 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D226">
-        <v>7.21255531764</v>
+        <v>12666447.5745149</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4108,10 +4108,10 @@
         <v>8</v>
       </c>
       <c r="C227" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D227">
-        <v>4.946461751422</v>
+        <v>12788630.800263</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4122,10 +4122,10 @@
         <v>8</v>
       </c>
       <c r="C228" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D228">
-        <v>4.041049938286</v>
+        <v>12843454.5550535</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4136,10 +4136,10 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D229">
-        <v>3.026419061992</v>
+        <v>12983757.1695154</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4150,10 +4150,10 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D230">
-        <v>3.863362970228</v>
+        <v>13049787.3583873</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4164,10 +4164,10 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D231">
-        <v>3.387115538055</v>
+        <v>13282702.0269995</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4178,10 +4178,10 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D232">
-        <v>3.68084046514</v>
+        <v>13278477.1999108</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4192,10 +4192,10 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D233">
-        <v>4.63943634059</v>
+        <v>13461668.5573064</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4206,10 +4206,10 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D234">
-        <v>2.774162958262</v>
+        <v>13655223.9354621</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4220,10 +4220,10 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D235">
-        <v>3.925600199098</v>
+        <v>13651185.8264888</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4234,10 +4234,10 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D236">
-        <v>2.545887318465</v>
+        <v>13804633.9425356</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4248,10 +4248,10 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D237">
-        <v>2.268452635295</v>
+        <v>13803748.7139758</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4262,10 +4262,10 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D238">
-        <v>2.940234373012</v>
+        <v>13964070.1706835</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4276,10 +4276,10 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D239">
-        <v>2.82178973071234</v>
+        <v>14051912.757931</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4290,10 +4290,10 @@
         <v>8</v>
       </c>
       <c r="C240" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D240">
-        <v>5.17205342293405</v>
+        <v>14194171.6854885</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4304,10 +4304,10 @@
         <v>8</v>
       </c>
       <c r="C241" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D241">
-        <v>4.52696119297973</v>
+        <v>14517685.9718302</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4318,10 +4318,10 @@
         <v>8</v>
       </c>
       <c r="C242" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D242">
-        <v>4.99090863730258</v>
+        <v>14596218.2082708</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4332,10 +4332,10 @@
         <v>8</v>
       </c>
       <c r="C243" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D243">
-        <v>-0.79323065804966</v>
+        <v>14753230.8854728</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4346,10 +4346,10 @@
         <v>8</v>
       </c>
       <c r="C244" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D244">
-        <v>-8.90602026709497</v>
+        <v>14081579.164023</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4360,10 +4360,10 @@
         <v>8</v>
       </c>
       <c r="C245" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D245">
-        <v>-7.45183804761752</v>
+        <v>13224737.9168658</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4374,10 +4374,10 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D246">
-        <v>-6.34352251849618</v>
+        <v>13508531.6663136</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4388,10 +4388,10 @@
         <v>8</v>
       </c>
       <c r="C247" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D247">
-        <v>0.384268140325819</v>
+        <v>13817356.3620471</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4402,10 +4402,10 @@
         <v>8</v>
       </c>
       <c r="C248" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D248">
-        <v>8.05085883546743</v>
+        <v>14135690.1864051</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4416,10 +4416,10 @@
         <v>8</v>
       </c>
       <c r="C249" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D249">
-        <v>7.35350244267947</v>
+        <v>14289442.8979132</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4430,10 +4430,10 @@
         <v>8</v>
       </c>
       <c r="C250" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D250">
-        <v>8.280136301370581</v>
+        <v>14501881.8723661</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4444,10 +4444,10 @@
         <v>8</v>
       </c>
       <c r="C251" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D251">
-        <v>6.20806380282288</v>
+        <v>14961452.3020707</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4458,10 +4458,10 @@
         <v>8</v>
       </c>
       <c r="C252" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D252">
-        <v>7.58361466665123</v>
+        <v>15013242.8521465</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4472,10 +4472,10 @@
         <v>8</v>
       </c>
       <c r="C253" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D253">
-        <v>8.18946940237784</v>
+        <v>15373099.1853021</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4486,10 +4486,10 @@
         <v>8</v>
       </c>
       <c r="C254" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D254">
-        <v>7.82390615805519</v>
+        <v>15689509.0510725</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4500,10 +4500,10 @@
         <v>8</v>
       </c>
       <c r="C255" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D255">
-        <v>9.130385130168699</v>
+        <v>16132022.2900669</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4514,10 +4514,10 @@
         <v>8</v>
       </c>
       <c r="C256" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D256">
-        <v>7.30511732023689</v>
+        <v>16384009.745075</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4528,10 +4528,10 @@
         <v>8</v>
       </c>
       <c r="C257" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D257">
-        <v>5.66962923784408</v>
+        <v>16496122.1165448</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4542,10 +4542,10 @@
         <v>8</v>
       </c>
       <c r="C258" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D258">
-        <v>2.95526871889429</v>
+        <v>16579046.0435063</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4556,10 +4556,10 @@
         <v>8</v>
       </c>
       <c r="C259" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D259">
-        <v>2.28134278006308</v>
+        <v>16608766.8985303</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4570,10 +4570,10 @@
         <v>8</v>
       </c>
       <c r="C260" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D260">
-        <v>2.31184196416569</v>
+        <v>16757785.1684791</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4584,10 +4584,10 @@
         <v>8</v>
       </c>
       <c r="C261" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D261">
-        <v>2.76026205302955</v>
+        <v>16877486.3900951</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4598,10 +4598,10 @@
         <v>8</v>
       </c>
       <c r="C262" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D262">
-        <v>3.60307738543223</v>
+        <v>17036671.1601995</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4612,10 +4612,10 @@
         <v>8</v>
       </c>
       <c r="C263" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D263">
-        <v>4.77449013439415</v>
+        <v>17207193.6226504</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4626,10 +4626,10 @@
         <v>8</v>
       </c>
       <c r="C264" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D264">
-        <v>5.38361125971189</v>
+        <v>17557883.9680911</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4640,10 +4640,10 @@
         <v>8</v>
       </c>
       <c r="C265" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D265">
-        <v>5.54103197518632</v>
+        <v>17786104.6477486</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4654,10 +4654,10 @@
         <v>8</v>
       </c>
       <c r="C266" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D266">
-        <v>3.31780623938527</v>
+        <v>17980678.5566935</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4668,10 +4668,10 @@
         <v>8</v>
       </c>
       <c r="C267" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D267">
-        <v>1.93372618334094</v>
+        <v>17778094.9662858</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4682,10 +4682,10 @@
         <v>8</v>
       </c>
       <c r="C268" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D268">
-        <v>-0.16026581711307</v>
+        <v>17897405.3676227</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4696,10 +4696,10 @@
         <v>8</v>
       </c>
       <c r="C269" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D269">
-        <v>-1.43962269408871</v>
+        <v>17757599.6018023</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4710,10 +4710,10 @@
         <v>8</v>
       </c>
       <c r="C270" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D270">
-        <v>-1.17844704105756</v>
+        <v>17721824.6276402</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4724,10 +4724,10 @@
         <v>8</v>
       </c>
       <c r="C271" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D271">
-        <v>-2.45068446167212</v>
+        <v>17568589.5321992</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4738,10 +4738,10 @@
         <v>8</v>
       </c>
       <c r="C272" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D272">
-        <v>-0.598660046362403</v>
+        <v>17458796.4352359</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4752,10 +4752,10 @@
         <v>8</v>
       </c>
       <c r="C273" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D273">
-        <v>0.51581591724719</v>
+        <v>17651291.9477933</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4766,10 +4766,10 @@
         <v>8</v>
       </c>
       <c r="C274" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D274">
-        <v>1.60705827097298</v>
+        <v>17813236.6198962</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4780,10 +4780,10 @@
         <v>8</v>
       </c>
       <c r="C275" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D275">
-        <v>2.23279440436086</v>
+        <v>17850927.0033697</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -4794,10 +4794,10 @@
         <v>8</v>
       </c>
       <c r="C276" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D276">
-        <v>1.2222144902893</v>
+        <v>17848615.4651106</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4808,10 +4808,10 @@
         <v>8</v>
       </c>
       <c r="C277" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D277">
-        <v>0.360536830608692</v>
+        <v>17867028.5957025</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -4822,10 +4822,10 @@
         <v>8</v>
       </c>
       <c r="C278" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D278">
-        <v>1.05373435141878</v>
+        <v>17877459.8986344</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -4836,10 +4836,10 @@
         <v>8</v>
       </c>
       <c r="C279" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D279">
-        <v>2.37903473569607</v>
+        <v>18039028.3532509</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -4850,10 +4850,10 @@
         <v>8</v>
       </c>
       <c r="C280" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D280">
-        <v>3.65219181426818</v>
+        <v>18273240.2268664</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -4864,10 +4864,10 @@
         <v>8</v>
       </c>
       <c r="C281" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D281">
-        <v>3.53889466794848</v>
+        <v>18519566.7515277</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4878,10 +4878,10 @@
         <v>8</v>
       </c>
       <c r="C282" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D282">
-        <v>3.70356751504026</v>
+        <v>18510124.3737518</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4892,10 +4892,10 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D283">
-        <v>2.60067983826201</v>
+        <v>18707115.9473708</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4906,10 +4906,10 @@
         <v>8</v>
       </c>
       <c r="C284" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D284">
-        <v>1.2707471104889</v>
+        <v>18748468.7012437</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -4920,10 +4920,10 @@
         <v>8</v>
       </c>
       <c r="C285" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D285">
-        <v>2.33881957144219</v>
+        <v>18754903.6108978</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -4934,10 +4934,10 @@
         <v>8</v>
       </c>
       <c r="C286" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D286">
-        <v>3.13679633638488</v>
+        <v>18943042.7853034</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4948,10 +4948,10 @@
         <v>8</v>
       </c>
       <c r="C287" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D287">
-        <v>4.96450995950648</v>
+        <v>19293920.0750512</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -4962,10 +4962,10 @@
         <v>8</v>
       </c>
       <c r="C288" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D288">
-        <v>5.79064684392698</v>
+        <v>19679238.2971719</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -4976,10 +4976,10 @@
         <v>8</v>
       </c>
       <c r="C289" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D289">
-        <v>5.0069853019614</v>
+        <v>19840933.8449238</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -4990,10 +4990,10 @@
         <v>8</v>
       </c>
       <c r="C290" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D290">
-        <v>3.4734293101135</v>
+        <v>19891518.1533078</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5004,10 +5004,10 @@
         <v>8</v>
       </c>
       <c r="C291" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D291">
-        <v>2.1911511188615</v>
+        <v>19964080.7500079</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5018,10 +5018,10 @@
         <v>8</v>
       </c>
       <c r="C292" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D292">
-        <v>1.98094374606039</v>
+        <v>20110440.1473038</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5032,10 +5032,10 @@
         <v>8</v>
       </c>
       <c r="C293" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D293">
-        <v>2.08638509222026</v>
+        <v>20233971.5830848</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5046,10 +5046,10 @@
         <v>8</v>
       </c>
       <c r="C294" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D294">
-        <v>1.98244766529379</v>
+        <v>20306531.8226747</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5060,10 +5060,10 @@
         <v>8</v>
       </c>
       <c r="C295" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D295">
-        <v>1.17662646739099</v>
+        <v>20359858.2027338</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5074,10 +5074,10 @@
         <v>8</v>
       </c>
       <c r="C296" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D296">
-        <v>1.35306347127755</v>
+        <v>20347064.9087858</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5088,10 +5088,10 @@
         <v>8</v>
       </c>
       <c r="C297" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D297">
-        <v>1.05309784689729</v>
+        <v>20507750.0613642</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5102,10 +5102,10 @@
         <v>8</v>
       </c>
       <c r="C298" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D298">
-        <v>-0.790533290813328</v>
+        <v>20520379.4720788</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5116,10 +5116,10 @@
         <v>8</v>
       </c>
       <c r="C299" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D299">
-        <v>-6.83668409737537</v>
+        <v>20198906.7456788</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5130,10 +5130,10 @@
         <v>8</v>
       </c>
       <c r="C300" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D300">
-        <v>-9.15077381943412</v>
+        <v>18956000.3578842</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5144,10 +5144,10 @@
         <v>8</v>
       </c>
       <c r="C301" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D301">
-        <v>-5.9041180355529</v>
+        <v>18631132.2377939</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5158,10 +5158,10 @@
         <v>8</v>
       </c>
       <c r="C302" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D302">
-        <v>-2.30979409261153</v>
+        <v>19308832.0467039</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5172,10 +5172,10 @@
         <v>8</v>
       </c>
       <c r="C303" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D303">
-        <v>4.54763778051975</v>
+        <v>19732353.590895</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5186,10 +5186,10 @@
         <v>8</v>
       </c>
       <c r="C304" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D304">
-        <v>7.48990914911801</v>
+        <v>19818050.5918348</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5200,10 +5200,10 @@
         <v>8</v>
       </c>
       <c r="C305" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D305">
-        <v>4.71371503270891</v>
+        <v>20026587.1158567</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5214,10 +5214,10 @@
         <v>8</v>
       </c>
       <c r="C306" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D306">
-        <v>3.31857820009092</v>
+        <v>20218995.3655299</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5228,10 +5228,10 @@
         <v>8</v>
       </c>
       <c r="C307" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D307">
-        <v>3.60742656102238</v>
+        <v>20387187.1755273</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5242,10 +5242,10 @@
         <v>8</v>
       </c>
       <c r="C308" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D308">
-        <v>2.80151316822362</v>
+        <v>20532972.2127615</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5256,10 +5256,10 @@
         <v>8</v>
       </c>
       <c r="C309" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D309">
-        <v>3.75173816701016</v>
+        <v>20587634.5910532</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5270,10 +5270,10 @@
         <v>8</v>
       </c>
       <c r="C310" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D310">
-        <v>3.64143090194049</v>
+        <v>20977559.1316445</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5284,10 +5284,10 @@
         <v>8</v>
       </c>
       <c r="C311" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D311">
-        <v>3.86599371924852</v>
+        <v>21129572.5093734</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5298,10 +5298,10 @@
         <v>8</v>
       </c>
       <c r="C312" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D312">
-        <v>4.22923821814714</v>
+        <v>21326775.6288819</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5312,10 +5312,10 @@
         <v>8</v>
       </c>
       <c r="C313" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D313">
-        <v>2.57446993508279</v>
+        <v>21458334.7013905</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5326,10 +5326,10 @@
         <v>8</v>
       </c>
       <c r="C314" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D314">
-        <v>2.62813644470874</v>
+        <v>21517620.0846029</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5340,10 +5340,10 @@
         <v>8</v>
       </c>
       <c r="C315" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D315">
-        <v>1.76544737576225</v>
+        <v>21684886.5051034</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5354,10 +5354,10 @@
         <v>8</v>
       </c>
       <c r="C316" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D316">
-        <v>0.734092112939644</v>
+        <v>21703288.6295567</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -5368,10 +5368,10 @@
         <v>8</v>
       </c>
       <c r="C317" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D317">
-        <v>1.08422140469493</v>
+        <v>21615858.6440016</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -5382,10 +5382,10 @@
         <v>8</v>
       </c>
       <c r="C318" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D318">
-        <v>0.79716261909978</v>
+        <v>21750918.7273411</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -5396,10 +5396,10 @@
         <v>8</v>
       </c>
       <c r="C319" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D319">
-        <v>1.38777414908504</v>
+        <v>21857750.3143163</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -5410,10 +5410,10 @@
         <v>8</v>
       </c>
       <c r="C320" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D320">
-        <v>3.07264160296593</v>
+        <v>22004481.258659</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -5424,10 +5424,10 @@
         <v>8</v>
       </c>
       <c r="C321" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D321">
-        <v>2.61374383912148</v>
+        <v>22280036.5095355</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -5438,10 +5438,10 @@
         <v>8</v>
       </c>
       <c r="C322" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D322">
-        <v>2.97902951468255</v>
+        <v>22319432.0255293</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -5452,10 +5452,10 @@
         <v>8</v>
       </c>
       <c r="C323" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D323">
-        <v>2.8043517721958</v>
+        <v>22508899.1474254</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -5466,10 +5466,10 @@
         <v>8</v>
       </c>
       <c r="C324" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D324">
-        <v>2.40274834784488</v>
+        <v>22621564.3187987</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -5480,10 +5480,10 @@
         <v>8</v>
       </c>
       <c r="C325" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D325">
-        <v>3.43342950498592</v>
+        <v>22815369.7186676</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -5494,10 +5494,10 @@
         <v>8</v>
       </c>
       <c r="C326" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D326">
-        <v>2.25841123276102</v>
+        <v>23085753.9900391</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -5508,10 +5508,10 @@
         <v>8</v>
       </c>
       <c r="C327" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D327">
-        <v>1.60074321781179</v>
+        <v>23017242.6541417</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -5522,10 +5522,10 @@
         <v>8</v>
       </c>
       <c r="C328" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D328">
-        <v>1.23209011957058</v>
+        <v>22983677.4753948</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -5536,10 +5536,10 @@
         <v>8</v>
       </c>
       <c r="C329" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D329">
-        <v>0.914896692320867</v>
+        <v>23096475.6347148</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5550,10 +5550,10 @@
         <v>8</v>
       </c>
       <c r="C330" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D330">
-        <v>2.34308418716372</v>
+        <v>23296964.7896913</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5564,10 +5564,10 @@
         <v>8</v>
       </c>
       <c r="C331" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D331">
-        <v>3.10494748579455</v>
+        <v>23556556.027092</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5578,10 +5578,10 @@
         <v>8</v>
       </c>
       <c r="C332" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D332">
-        <v>2.69127195680336</v>
+        <v>23697308.5913102</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5592,10 +5592,10 @@
         <v>8</v>
       </c>
       <c r="C333" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D333">
-        <v>1.21540031757053</v>
+        <v>23718064.6064818</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5606,10 +5606,10 @@
         <v>8</v>
       </c>
       <c r="C334" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D334">
-        <v>1.49405913504092</v>
+        <v>23580116.1737295</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5620,10 +5620,10 @@
         <v>8</v>
       </c>
       <c r="C335" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D335">
-        <v>2.15199522354916</v>
+        <v>23908504.9043158</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5634,10 +5634,10 @@
         <v>8</v>
       </c>
       <c r="C336" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D336">
-        <v>1.76149662564593</v>
+        <v>24207273.5403049</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5648,10 +5648,10 @@
         <v>8</v>
       </c>
       <c r="C337" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D337">
-        <v>2.76841142174641</v>
+        <v>24135857.5141935</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5662,10 +5662,10 @@
         <v>8</v>
       </c>
       <c r="C338" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D338">
-        <v>1.1632916142895</v>
+        <v>24232910.8031441</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5676,10 +5676,10 @@
         <v>8</v>
       </c>
       <c r="C339" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D339">
-        <v>-0.0597420902482826</v>
+        <v>24186630.5369697</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5690,10 +5690,10 @@
         <v>8</v>
       </c>
       <c r="C340" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D340">
-        <v>-0.06804254524888349</v>
+        <v>24192811.6090998</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5704,10 +5704,10 @@
         <v>8</v>
       </c>
       <c r="C341" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D341">
-        <v>-0.438725353203986</v>
+        <v>24119434.8624232</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -5718,10 +5718,10 @@
         <v>8</v>
       </c>
       <c r="C342" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D342">
-        <v>-0.990298968647934</v>
+        <v>24126594.8796314</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5732,10 +5732,10 @@
         <v>8</v>
       </c>
       <c r="C343" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D343">
-        <v>-2.21915580376183</v>
+        <v>23947110.5842114</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5746,10 +5746,10 @@
         <v>8</v>
       </c>
       <c r="C344" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D344">
-        <v>-20.4706531046103</v>
+        <v>23655935.4261833</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5760,10 +5760,10 @@
         <v>8</v>
       </c>
       <c r="C345" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D345">
-        <v>-8.114518275349379</v>
+        <v>19182029.0209441</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -5774,10 +5774,10 @@
         <v>8</v>
       </c>
       <c r="C346" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D346">
-        <v>-3.44681318996457</v>
+        <v>22168837.9289042</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -5788,10 +5788,10 @@
         <v>8</v>
       </c>
       <c r="C347" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D347">
-        <v>-1.52021122601162</v>
+        <v>23121698.4179794</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -5802,10 +5802,10 @@
         <v>8</v>
       </c>
       <c r="C348" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D348">
-        <v>22.5198903326093</v>
+        <v>23296315.2402164</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -5816,10 +5816,10 @@
         <v>8</v>
       </c>
       <c r="C349" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D349">
-        <v>5.10235700045289</v>
+        <v>23501800.92003</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -5830,10 +5830,10 @@
         <v>8</v>
       </c>
       <c r="C350" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D350">
-        <v>1.94868830643919</v>
+        <v>23299971.1828887</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -5844,10 +5844,10 @@
         <v>8</v>
       </c>
       <c r="C351" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D351">
-        <v>2.64624871085353</v>
+        <v>23572268.2513007</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -5858,10 +5858,10 @@
         <v>8</v>
       </c>
       <c r="C352" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D352">
-        <v>2.90804674355962</v>
+        <v>23912793.681937</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -5872,10 +5872,10 @@
         <v>8</v>
       </c>
       <c r="C353" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D353">
-        <v>4.60008757551484</v>
+        <v>24185244.2763628</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -5886,10 +5886,10 @@
         <v>8</v>
       </c>
       <c r="C354" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D354">
-        <v>4.67400505541721</v>
+        <v>24371790.2623713</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -5900,10 +5900,10 @@
         <v>8</v>
       </c>
       <c r="C355" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D355">
-        <v>3.77179397115653</v>
+        <v>24674037.261043</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -5914,10 +5914,10 @@
         <v>8</v>
       </c>
       <c r="C356" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D356">
-        <v>3.35357333870012</v>
+        <v>24814734.9923674</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -5928,10 +5928,10 @@
         <v>8</v>
       </c>
       <c r="C357" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D357">
-        <v>3.21223901248618</v>
+        <v>24996314.1803144</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -5942,10 +5942,10 @@
         <v>8</v>
       </c>
       <c r="C358" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D358">
-        <v>2.13921571997775</v>
+        <v>25154670.4172205</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -5956,10 +5956,10 @@
         <v>8</v>
       </c>
       <c r="C359" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D359">
-        <v>1.97982146977274</v>
+        <v>25201868.1448844</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -5970,10 +5970,10 @@
         <v>8</v>
       </c>
       <c r="C360" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D360">
-        <v>1.07992915834643</v>
+        <v>25306022.4434135</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -5984,10 +5984,10 @@
         <v>8</v>
       </c>
       <c r="C361" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D361">
-        <v>1.4335903209204</v>
+        <v>25266256.6656595</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -5998,10 +5998,10 @@
         <v>8</v>
       </c>
       <c r="C362" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D362">
-        <v>0.352984350732571</v>
+        <v>25515285.3375812</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6012,10 +6012,10 @@
         <v>8</v>
       </c>
       <c r="C363" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D363">
-        <v>0.713955793035045</v>
+        <v>25290826.7955281</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6026,10 +6026,10 @@
         <v>8</v>
       </c>
       <c r="C364" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D364">
-        <v>0.848255135504099</v>
+        <v>25486696.256635</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6040,10 +6040,10 @@
         <v>8</v>
       </c>
       <c r="C365" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D365">
-        <v>-0.240685690253069</v>
+        <v>25480578.9853756</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6054,10 +6054,10 @@
         <v>8</v>
       </c>
       <c r="C366" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D366">
-        <v>1.59606943658511</v>
+        <v>25453873.6969464</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6068,10 +6068,10 @@
         <v>8</v>
       </c>
       <c r="C367" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D367">
-        <v>0.469878458114494</v>
+        <v>25694485.9522712</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6082,24 +6082,24 @@
         <v>8</v>
       </c>
       <c r="C368" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D368">
-        <v>1.92544131907043</v>
+        <v>25606452.75203</v>
       </c>
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B369" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C369" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D369">
-        <v>10290879.5792174</v>
+        <v>25971192.5814984</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6110,10 +6110,10 @@
         <v>9</v>
       </c>
       <c r="C370" t="s">
-        <v>10</v>
+        <v>193</v>
       </c>
       <c r="D370">
-        <v>10320081.622513</v>
+        <v>0.283766252154</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6124,10 +6124,10 @@
         <v>9</v>
       </c>
       <c r="C371" t="s">
-        <v>11</v>
+        <v>194</v>
       </c>
       <c r="D371">
-        <v>10561154.1603744</v>
+        <v>2.33595572864</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6138,10 +6138,10 @@
         <v>9</v>
       </c>
       <c r="C372" t="s">
-        <v>12</v>
+        <v>195</v>
       </c>
       <c r="D372">
-        <v>10891932.5257052</v>
+        <v>3.132028567217</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6152,10 +6152,10 @@
         <v>9</v>
       </c>
       <c r="C373" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D373">
-        <v>11229886.8424759</v>
+        <v>3.102794806827</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6166,10 +6166,10 @@
         <v>9</v>
       </c>
       <c r="C374" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D374">
-        <v>11538405.6443222</v>
+        <v>2.747301074124</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6180,10 +6180,10 @@
         <v>9</v>
       </c>
       <c r="C375" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D375">
-        <v>11604826.3039261</v>
+        <v>0.5756485051</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6194,10 +6194,10 @@
         <v>9</v>
       </c>
       <c r="C376" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D376">
-        <v>11729803.171789</v>
+        <v>1.076938720062</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6208,10 +6208,10 @@
         <v>9</v>
       </c>
       <c r="C377" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D377">
-        <v>11616894.6298516</v>
+        <v>-0.962578316821</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6222,10 +6222,10 @@
         <v>9</v>
       </c>
       <c r="C378" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D378">
-        <v>11626873.1619578</v>
+        <v>0.085896725624</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6236,10 +6236,10 @@
         <v>9</v>
       </c>
       <c r="C379" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D379">
-        <v>11561013.3281264</v>
+        <v>-0.566444932477</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6250,10 +6250,10 @@
         <v>9</v>
       </c>
       <c r="C380" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D380">
-        <v>11281559.9740545</v>
+        <v>-2.417204670044</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6264,10 +6264,10 @@
         <v>9</v>
       </c>
       <c r="C381" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D381">
-        <v>11080619.373705</v>
+        <v>-1.781141976922</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6278,10 +6278,10 @@
         <v>9</v>
       </c>
       <c r="C382" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D382">
-        <v>10880722.4686874</v>
+        <v>-1.80402284634</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6292,10 +6292,10 @@
         <v>9</v>
       </c>
       <c r="C383" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D383">
-        <v>10920827.7463505</v>
+        <v>0.368590208771</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6306,10 +6306,10 @@
         <v>9</v>
       </c>
       <c r="C384" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D384">
-        <v>11067793.5127387</v>
+        <v>1.345738343298</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -6320,10 +6320,10 @@
         <v>9</v>
       </c>
       <c r="C385" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D385">
-        <v>11375656.7989038</v>
+        <v>2.781613930643</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -6334,10 +6334,10 @@
         <v>9</v>
       </c>
       <c r="C386" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D386">
-        <v>11238037.8209625</v>
+        <v>-1.209767316069</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -6348,10 +6348,10 @@
         <v>9</v>
       </c>
       <c r="C387" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D387">
-        <v>11446495.5985385</v>
+        <v>1.85493037928</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -6362,10 +6362,10 @@
         <v>9</v>
       </c>
       <c r="C388" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D388">
-        <v>11430607.9199105</v>
+        <v>-0.138799499735</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -6376,10 +6376,10 @@
         <v>9</v>
       </c>
       <c r="C389" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D389">
-        <v>11612093.0714764</v>
+        <v>1.587712157022</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -6390,10 +6390,10 @@
         <v>9</v>
       </c>
       <c r="C390" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D390">
-        <v>11546940.1681099</v>
+        <v>-0.56107803275</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -6404,10 +6404,10 @@
         <v>9</v>
       </c>
       <c r="C391" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D391">
-        <v>11605606.6558549</v>
+        <v>0.508069556877</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -6418,10 +6418,10 @@
         <v>9</v>
       </c>
       <c r="C392" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D392">
-        <v>11581710.1937746</v>
+        <v>-0.205904463152</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -6432,10 +6432,10 @@
         <v>9</v>
       </c>
       <c r="C393" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D393">
-        <v>11345667.8923105</v>
+        <v>-2.03806085211</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -6446,10 +6446,10 @@
         <v>9</v>
       </c>
       <c r="C394" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D394">
-        <v>11204328.8187642</v>
+        <v>-1.24575366464</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -6460,10 +6460,10 @@
         <v>9</v>
       </c>
       <c r="C395" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D395">
-        <v>11024508.0911471</v>
+        <v>-1.604921905862</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -6474,10 +6474,10 @@
         <v>9</v>
       </c>
       <c r="C396" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D396">
-        <v>10952435.2344758</v>
+        <v>-0.653751224775</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -6488,10 +6488,10 @@
         <v>9</v>
       </c>
       <c r="C397" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D397">
-        <v>11063181.1901069</v>
+        <v>1.011153713856</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -6502,10 +6502,10 @@
         <v>9</v>
       </c>
       <c r="C398" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D398">
-        <v>11370009.3174828</v>
+        <v>2.773416814779</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -6516,10 +6516,10 @@
         <v>9</v>
       </c>
       <c r="C399" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D399">
-        <v>11462394.4833155</v>
+        <v>0.812533774187</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -6530,10 +6530,10 @@
         <v>9</v>
       </c>
       <c r="C400" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D400">
-        <v>11560459.095168</v>
+        <v>0.855533387856</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -6544,10 +6544,10 @@
         <v>9</v>
       </c>
       <c r="C401" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D401">
-        <v>11480960.8468467</v>
+        <v>-0.68767379969</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6558,10 +6558,10 @@
         <v>9</v>
       </c>
       <c r="C402" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D402">
-        <v>11443043.0968728</v>
+        <v>-0.330266346865</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -6572,10 +6572,10 @@
         <v>9</v>
       </c>
       <c r="C403" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D403">
-        <v>11454697.0014456</v>
+        <v>0.101842704551</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -6586,10 +6586,10 @@
         <v>9</v>
       </c>
       <c r="C404" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D404">
-        <v>11630199.704692</v>
+        <v>1.532146186182</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6600,10 +6600,10 @@
         <v>9</v>
       </c>
       <c r="C405" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D405">
-        <v>11848345.9695141</v>
+        <v>1.875688039425</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -6614,10 +6614,10 @@
         <v>9</v>
       </c>
       <c r="C406" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D406">
-        <v>11833085.2899035</v>
+        <v>-0.128800084416</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -6628,10 +6628,10 @@
         <v>9</v>
       </c>
       <c r="C407" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D407">
-        <v>12057397.0014554</v>
+        <v>1.895631663733</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -6642,10 +6642,10 @@
         <v>9</v>
       </c>
       <c r="C408" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D408">
-        <v>11928295.8627131</v>
+        <v>-1.070721472692</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -6656,10 +6656,10 @@
         <v>9</v>
       </c>
       <c r="C409" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D409">
-        <v>12238101.5431228</v>
+        <v>2.597233368248</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -6670,10 +6670,10 @@
         <v>9</v>
       </c>
       <c r="C410" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D410">
-        <v>12479456.1158475</v>
+        <v>1.972156971196</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -6684,10 +6684,10 @@
         <v>9</v>
       </c>
       <c r="C411" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D411">
-        <v>12666447.5745149</v>
+        <v>1.498394296446</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -6698,10 +6698,10 @@
         <v>9</v>
       </c>
       <c r="C412" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D412">
-        <v>12788630.800263</v>
+        <v>0.96462109861</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -6712,10 +6712,10 @@
         <v>9</v>
       </c>
       <c r="C413" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D413">
-        <v>12843454.5550535</v>
+        <v>0.428691355992</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -6726,10 +6726,10 @@
         <v>9</v>
       </c>
       <c r="C414" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D414">
-        <v>12983757.1695154</v>
+        <v>1.092405581851</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -6740,10 +6740,10 @@
         <v>9</v>
       </c>
       <c r="C415" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D415">
-        <v>13049787.3583873</v>
+        <v>0.5085599492490001</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -6754,10 +6754,10 @@
         <v>9</v>
       </c>
       <c r="C416" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D416">
-        <v>13282702.0269995</v>
+        <v>1.784815815121</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -6768,10 +6768,10 @@
         <v>9</v>
       </c>
       <c r="C417" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D417">
-        <v>13278477.1999108</v>
+        <v>-0.031806985357</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -6782,10 +6782,10 @@
         <v>9</v>
       </c>
       <c r="C418" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D418">
-        <v>13461668.5573064</v>
+        <v>1.379611190633</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -6796,10 +6796,10 @@
         <v>9</v>
       </c>
       <c r="C419" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D419">
-        <v>13655223.9354621</v>
+        <v>1.437826056493</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -6810,10 +6810,10 @@
         <v>9</v>
       </c>
       <c r="C420" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D420">
-        <v>13651185.8264888</v>
+        <v>-0.029571898582</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -6824,10 +6824,10 @@
         <v>9</v>
       </c>
       <c r="C421" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D421">
-        <v>13804633.9425356</v>
+        <v>1.088193382663</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -6838,10 +6838,10 @@
         <v>9</v>
       </c>
       <c r="C422" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D422">
-        <v>13803748.7139758</v>
+        <v>-0.00641254642089333</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -6852,10 +6852,10 @@
         <v>9</v>
       </c>
       <c r="C423" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D423">
-        <v>13964070.1706835</v>
+        <v>1.16143418740577</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -6866,10 +6866,10 @@
         <v>9</v>
       </c>
       <c r="C424" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D424">
-        <v>14051912.757931</v>
+        <v>0.629061485468034</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -6880,10 +6880,10 @@
         <v>9</v>
       </c>
       <c r="C425" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D425">
-        <v>14194171.6854885</v>
+        <v>1.01238123242125</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -6894,10 +6894,10 @@
         <v>9</v>
       </c>
       <c r="C426" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D426">
-        <v>14517685.9718302</v>
+        <v>2.27920510974548</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -6908,10 +6908,10 @@
         <v>9</v>
       </c>
       <c r="C427" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D427">
-        <v>14596218.2082708</v>
+        <v>0.540941831866189</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -6922,10 +6922,10 @@
         <v>9</v>
       </c>
       <c r="C428" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D428">
-        <v>14753230.8854728</v>
+        <v>1.07570793312087</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -6936,10 +6936,10 @@
         <v>9</v>
       </c>
       <c r="C429" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D429">
-        <v>14081579.164023</v>
+        <v>-4.55257378308341</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -6950,10 +6950,10 @@
         <v>9</v>
       </c>
       <c r="C430" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D430">
-        <v>13224737.9168658</v>
+        <v>-6.08483776696255</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -6964,10 +6964,10 @@
         <v>9</v>
       </c>
       <c r="C431" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D431">
-        <v>13508531.6663136</v>
+        <v>2.14593099108506</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -6978,10 +6978,10 @@
         <v>9</v>
       </c>
       <c r="C432" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D432">
-        <v>13817356.3620471</v>
+        <v>2.28614555128609</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -6992,10 +6992,10 @@
         <v>9</v>
       </c>
       <c r="C433" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D433">
-        <v>14135690.1864051</v>
+        <v>2.303869249782</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7006,10 +7006,10 @@
         <v>9</v>
       </c>
       <c r="C434" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D434">
-        <v>14289442.8979132</v>
+        <v>1.08769157699828</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7020,10 +7020,10 @@
         <v>9</v>
       </c>
       <c r="C435" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D435">
-        <v>14501881.8723661</v>
+        <v>1.48668479219665</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7034,10 +7034,10 @@
         <v>9</v>
       </c>
       <c r="C436" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D436">
-        <v>14961452.3020707</v>
+        <v>3.16903994770726</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7048,10 +7048,10 @@
         <v>9</v>
       </c>
       <c r="C437" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D437">
-        <v>15013242.8521465</v>
+        <v>0.346159911686068</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7062,10 +7062,10 @@
         <v>9</v>
       </c>
       <c r="C438" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D438">
-        <v>15373099.1853021</v>
+        <v>2.39692607852639</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7076,10 +7076,10 @@
         <v>9</v>
       </c>
       <c r="C439" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D439">
-        <v>15689509.0510725</v>
+        <v>2.05820480279549</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7090,10 +7090,10 @@
         <v>9</v>
       </c>
       <c r="C440" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D440">
-        <v>16132022.2900669</v>
+        <v>2.82044031813825</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7104,10 +7104,10 @@
         <v>9</v>
       </c>
       <c r="C441" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D441">
-        <v>16384009.745075</v>
+        <v>1.56203264833857</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7118,10 +7118,10 @@
         <v>9</v>
       </c>
       <c r="C442" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D442">
-        <v>16496122.1165448</v>
+        <v>0.684279204017809</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7132,10 +7132,10 @@
         <v>9</v>
       </c>
       <c r="C443" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D443">
-        <v>16579046.0435063</v>
+        <v>0.502687397532852</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7146,10 +7146,10 @@
         <v>9</v>
       </c>
       <c r="C444" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D444">
-        <v>16608766.8985303</v>
+        <v>0.179267582380844</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7160,10 +7160,10 @@
         <v>9</v>
       </c>
       <c r="C445" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D445">
-        <v>16757785.1684791</v>
+        <v>0.897226572322992</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7174,10 +7174,10 @@
         <v>9</v>
       </c>
       <c r="C446" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D446">
-        <v>16877486.3900951</v>
+        <v>0.714302161130186</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7188,10 +7188,10 @@
         <v>9</v>
       </c>
       <c r="C447" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D447">
-        <v>17036671.1601995</v>
+        <v>0.943178186757844</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7202,10 +7202,10 @@
         <v>9</v>
       </c>
       <c r="C448" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D448">
-        <v>17207193.6226504</v>
+        <v>1.0009142093983</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -7216,10 +7216,10 @@
         <v>9</v>
       </c>
       <c r="C449" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D449">
-        <v>17557883.9680911</v>
+        <v>2.03804497776485</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -7230,10 +7230,10 @@
         <v>9</v>
       </c>
       <c r="C450" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D450">
-        <v>17786104.6477486</v>
+        <v>1.29981881684751</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -7244,10 +7244,10 @@
         <v>9</v>
       </c>
       <c r="C451" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D451">
-        <v>17980678.5566935</v>
+        <v>1.09396583905476</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -7258,10 +7258,10 @@
         <v>9</v>
       </c>
       <c r="C452" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D452">
-        <v>17778094.9662858</v>
+        <v>-1.12667377801651</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -7272,10 +7272,10 @@
         <v>9</v>
       </c>
       <c r="C453" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D453">
-        <v>17897405.3676227</v>
+        <v>0.671109033690955</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -7286,10 +7286,10 @@
         <v>9</v>
       </c>
       <c r="C454" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D454">
-        <v>17757599.6018023</v>
+        <v>-0.781151026915413</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -7300,10 +7300,10 @@
         <v>9</v>
       </c>
       <c r="C455" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D455">
-        <v>17721824.6276402</v>
+        <v>-0.201462894559638</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -7314,10 +7314,10 @@
         <v>9</v>
       </c>
       <c r="C456" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D456">
-        <v>17568589.5321992</v>
+        <v>-0.864668840035819</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -7328,10 +7328,10 @@
         <v>9</v>
       </c>
       <c r="C457" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D457">
-        <v>17458796.4352359</v>
+        <v>-0.624939735555183</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -7342,10 +7342,10 @@
         <v>9</v>
       </c>
       <c r="C458" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D458">
-        <v>17651291.9477933</v>
+        <v>1.10257034768389</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -7356,10 +7356,10 @@
         <v>9</v>
       </c>
       <c r="C459" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D459">
-        <v>17813236.6198962</v>
+        <v>0.917466396124869</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -7370,10 +7370,10 @@
         <v>9</v>
       </c>
       <c r="C460" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D460">
-        <v>17850927.0033697</v>
+        <v>0.21158638532541</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -7384,10 +7384,10 @@
         <v>9</v>
       </c>
       <c r="C461" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D461">
-        <v>17848615.4651106</v>
+        <v>-0.0129491216823856</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -7398,10 +7398,10 @@
         <v>9</v>
       </c>
       <c r="C462" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D462">
-        <v>17867028.5957025</v>
+        <v>0.103162795052042</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -7412,10 +7412,10 @@
         <v>9</v>
       </c>
       <c r="C463" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D463">
-        <v>17877459.8986344</v>
+        <v>0.0583829755240336</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -7426,10 +7426,10 @@
         <v>9</v>
       </c>
       <c r="C464" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D464">
-        <v>18039028.3532509</v>
+        <v>0.903755094586115</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -7440,10 +7440,10 @@
         <v>9</v>
       </c>
       <c r="C465" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D465">
-        <v>18273240.2268664</v>
+        <v>1.29836191300899</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -7454,10 +7454,10 @@
         <v>9</v>
       </c>
       <c r="C466" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D466">
-        <v>18519566.7515277</v>
+        <v>1.34801776588662</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -7468,10 +7468,10 @@
         <v>9</v>
       </c>
       <c r="C467" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D467">
-        <v>18510124.3737518</v>
+        <v>-0.0509859539512238</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -7482,10 +7482,10 @@
         <v>9</v>
       </c>
       <c r="C468" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D468">
-        <v>18707115.9473708</v>
+        <v>1.06423689890676</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -7496,10 +7496,10 @@
         <v>9</v>
       </c>
       <c r="C469" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D469">
-        <v>18748468.7012437</v>
+        <v>0.221053603287841</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -7510,10 +7510,10 @@
         <v>9</v>
       </c>
       <c r="C470" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D470">
-        <v>18754903.6108978</v>
+        <v>0.0343223212340342</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -7524,10 +7524,10 @@
         <v>9</v>
       </c>
       <c r="C471" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D471">
-        <v>18943042.7853034</v>
+        <v>1.00314658133607</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -7538,10 +7538,10 @@
         <v>9</v>
       </c>
       <c r="C472" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D472">
-        <v>19293920.0750512</v>
+        <v>1.85227523225583</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -7552,10 +7552,10 @@
         <v>9</v>
       </c>
       <c r="C473" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D473">
-        <v>19679238.2971719</v>
+        <v>1.99709660152967</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -7566,10 +7566,10 @@
         <v>9</v>
       </c>
       <c r="C474" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D474">
-        <v>19840933.8449238</v>
+        <v>0.8216555199453059</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -7580,10 +7580,10 @@
         <v>9</v>
       </c>
       <c r="C475" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D475">
-        <v>19891518.1533078</v>
+        <v>0.254949231620664</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -7594,10 +7594,10 @@
         <v>9</v>
       </c>
       <c r="C476" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D476">
-        <v>19964080.7500079</v>
+        <v>0.364791647077151</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -7608,10 +7608,10 @@
         <v>9</v>
       </c>
       <c r="C477" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D477">
-        <v>20110440.1473038</v>
+        <v>0.733113631068847</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -7622,10 +7622,10 @@
         <v>9</v>
       </c>
       <c r="C478" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D478">
-        <v>20233971.5830848</v>
+        <v>0.614265201935723</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -7636,10 +7636,10 @@
         <v>9</v>
       </c>
       <c r="C479" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D479">
-        <v>20306531.8226747</v>
+        <v>0.358606017073577</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -7650,10 +7650,10 @@
         <v>9</v>
       </c>
       <c r="C480" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D480">
-        <v>20359858.2027338</v>
+        <v>0.262607029722108</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -7664,10 +7664,10 @@
         <v>9</v>
       </c>
       <c r="C481" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D481">
-        <v>20347064.9087858</v>
+        <v>-0.06283586958518519</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -7678,10 +7678,10 @@
         <v>9</v>
       </c>
       <c r="C482" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D482">
-        <v>20507750.0613642</v>
+        <v>0.789721531330129</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -7692,10 +7692,10 @@
         <v>9</v>
       </c>
       <c r="C483" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D483">
-        <v>20520379.4720788</v>
+        <v>0.0615835997455106</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -7706,10 +7706,10 @@
         <v>9</v>
       </c>
       <c r="C484" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D484">
-        <v>20198906.7456788</v>
+        <v>-1.56660224942435</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -7720,10 +7720,10 @@
         <v>9</v>
       </c>
       <c r="C485" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D485">
-        <v>18956000.3578842</v>
+        <v>-6.15333494749908</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -7734,10 +7734,10 @@
         <v>9</v>
       </c>
       <c r="C486" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D486">
-        <v>18631132.2377939</v>
+        <v>-1.71380098099217</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -7748,10 +7748,10 @@
         <v>9</v>
       </c>
       <c r="C487" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D487">
-        <v>19308832.0467039</v>
+        <v>3.63745906722332</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -7762,10 +7762,10 @@
         <v>9</v>
       </c>
       <c r="C488" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D488">
-        <v>19732353.590895</v>
+        <v>2.19340840070851</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -7776,10 +7776,10 @@
         <v>9</v>
       </c>
       <c r="C489" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D489">
-        <v>19818050.5918348</v>
+        <v>0.434296905055165</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -7790,10 +7790,10 @@
         <v>9</v>
       </c>
       <c r="C490" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D490">
-        <v>20026587.1158567</v>
+        <v>1.05225548323011</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -7804,10 +7804,10 @@
         <v>9</v>
       </c>
       <c r="C491" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D491">
-        <v>20218995.3655299</v>
+        <v>0.960764051109098</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -7818,10 +7818,10 @@
         <v>9</v>
       </c>
       <c r="C492" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D492">
-        <v>20387187.1755273</v>
+        <v>0.8318504799904149</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -7832,10 +7832,10 @@
         <v>9</v>
       </c>
       <c r="C493" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D493">
-        <v>20532972.2127615</v>
+        <v>0.715081663689232</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -7846,10 +7846,10 @@
         <v>9</v>
       </c>
       <c r="C494" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D494">
-        <v>20587634.5910532</v>
+        <v>0.266217563269899</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -7860,10 +7860,10 @@
         <v>9</v>
       </c>
       <c r="C495" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D495">
-        <v>20977559.1316445</v>
+        <v>1.89397445766184</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -7874,10 +7874,10 @@
         <v>9</v>
       </c>
       <c r="C496" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D496">
-        <v>21129572.5093734</v>
+        <v>0.724647594960603</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -7888,10 +7888,10 @@
         <v>9</v>
       </c>
       <c r="C497" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D497">
-        <v>21326775.6288819</v>
+        <v>0.933303877402247</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -7902,10 +7902,10 @@
         <v>9</v>
       </c>
       <c r="C498" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D498">
-        <v>21458334.7013905</v>
+        <v>0.616872774384314</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -7916,10 +7916,10 @@
         <v>9</v>
       </c>
       <c r="C499" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D499">
-        <v>21517620.0846029</v>
+        <v>0.276281379880605</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -7930,10 +7930,10 @@
         <v>9</v>
       </c>
       <c r="C500" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D500">
-        <v>21684886.5051034</v>
+        <v>0.77734628570838</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -7944,10 +7944,10 @@
         <v>9</v>
       </c>
       <c r="C501" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D501">
-        <v>21703288.6295567</v>
+        <v>0.08486152071383039</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -7958,10 +7958,10 @@
         <v>9</v>
       </c>
       <c r="C502" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D502">
-        <v>21615858.6440016</v>
+        <v>-0.402842108619583</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -7972,10 +7972,10 @@
         <v>9</v>
       </c>
       <c r="C503" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D503">
-        <v>21750918.7273411</v>
+        <v>0.6248194233865469</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -7986,10 +7986,10 @@
         <v>9</v>
       </c>
       <c r="C504" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D504">
-        <v>21857750.3143163</v>
+        <v>0.491158963510396</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -8000,10 +8000,10 @@
         <v>9</v>
       </c>
       <c r="C505" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D505">
-        <v>22004481.258659</v>
+        <v>0.67129938915349</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -8014,10 +8014,10 @@
         <v>9</v>
       </c>
       <c r="C506" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D506">
-        <v>22280036.5095355</v>
+        <v>1.25226878851354</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -8028,10 +8028,10 @@
         <v>9</v>
       </c>
       <c r="C507" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D507">
-        <v>22319432.0255293</v>
+        <v>0.176819799989736</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -8042,10 +8042,10 @@
         <v>9</v>
       </c>
       <c r="C508" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D508">
-        <v>22508899.1474254</v>
+        <v>0.8488886351560641</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -8056,10 +8056,10 @@
         <v>9</v>
       </c>
       <c r="C509" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D509">
-        <v>22621564.3187987</v>
+        <v>0.500536124114204</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -8070,10 +8070,10 @@
         <v>9</v>
       </c>
       <c r="C510" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D510">
-        <v>22815369.7186676</v>
+        <v>0.85672854952763</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -8084,10 +8084,10 @@
         <v>9</v>
       </c>
       <c r="C511" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D511">
-        <v>23085753.9900391</v>
+        <v>1.18509704074736</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -8098,10 +8098,10 @@
         <v>9</v>
       </c>
       <c r="C512" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D512">
-        <v>23017242.6541417</v>
+        <v>-0.296768890143062</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -8112,10 +8112,10 @@
         <v>9</v>
       </c>
       <c r="C513" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D513">
-        <v>22983677.4753948</v>
+        <v>-0.145826236666369</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -8126,10 +8126,10 @@
         <v>9</v>
       </c>
       <c r="C514" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D514">
-        <v>23096475.6347148</v>
+        <v>0.490775070441862</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -8140,10 +8140,10 @@
         <v>9</v>
       </c>
       <c r="C515" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D515">
-        <v>23296964.7896913</v>
+        <v>0.868050858266689</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -8154,10 +8154,10 @@
         <v>9</v>
       </c>
       <c r="C516" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D516">
-        <v>23556556.027092</v>
+        <v>1.11427063458311</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -8168,10 +8168,10 @@
         <v>9</v>
       </c>
       <c r="C517" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D517">
-        <v>23697308.5913102</v>
+        <v>0.597509092824611</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -8182,10 +8182,10 @@
         <v>9</v>
       </c>
       <c r="C518" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D518">
-        <v>23718064.6064818</v>
+        <v>0.0875880697237319</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -8196,10 +8196,10 @@
         <v>9</v>
       </c>
       <c r="C519" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D519">
-        <v>23580116.1737295</v>
+        <v>-0.581617577323745</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -8210,10 +8210,10 @@
         <v>9</v>
       </c>
       <c r="C520" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D520">
-        <v>23908504.9043158</v>
+        <v>1.3926510292267</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -8224,10 +8224,10 @@
         <v>9</v>
       </c>
       <c r="C521" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D521">
-        <v>24207273.5403049</v>
+        <v>1.24963328817425</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -8238,10 +8238,10 @@
         <v>9</v>
       </c>
       <c r="C522" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D522">
-        <v>24135857.5141935</v>
+        <v>-0.295018875184316</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -8252,10 +8252,10 @@
         <v>9</v>
       </c>
       <c r="C523" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D523">
-        <v>24232910.8031441</v>
+        <v>0.402112454026238</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -8266,10 +8266,10 @@
         <v>9</v>
       </c>
       <c r="C524" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D524">
-        <v>24186630.5369697</v>
+        <v>-0.190981044540461</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -8280,10 +8280,10 @@
         <v>9</v>
       </c>
       <c r="C525" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D525">
-        <v>24192811.6090998</v>
+        <v>0.0255557388229688</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -8294,10 +8294,10 @@
         <v>9</v>
       </c>
       <c r="C526" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D526">
-        <v>24119434.8624232</v>
+        <v>-0.303299789467226</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -8308,10 +8308,10 @@
         <v>9</v>
       </c>
       <c r="C527" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D527">
-        <v>24126594.8796314</v>
+        <v>0.0296856756762276</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -8322,10 +8322,10 @@
         <v>9</v>
       </c>
       <c r="C528" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D528">
-        <v>23947110.5842114</v>
+        <v>-0.743927173790804</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -8336,10 +8336,10 @@
         <v>9</v>
       </c>
       <c r="C529" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D529">
-        <v>23655935.4261833</v>
+        <v>-1.21590935576202</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -8350,10 +8350,10 @@
         <v>9</v>
       </c>
       <c r="C530" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D530">
-        <v>19182029.0209441</v>
+        <v>-18.9124053842627</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -8364,10 +8364,10 @@
         <v>9</v>
       </c>
       <c r="C531" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D531">
-        <v>22168837.9289042</v>
+        <v>15.5708705512797</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -8378,10 +8378,10 @@
         <v>9</v>
       </c>
       <c r="C532" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D532">
-        <v>23121698.4179794</v>
+        <v>4.29819773201932</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -8392,10 +8392,10 @@
         <v>9</v>
       </c>
       <c r="C533" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D533">
-        <v>23296315.2402164</v>
+        <v>0.75520759366543</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -8406,10 +8406,10 @@
         <v>9</v>
       </c>
       <c r="C534" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D534">
-        <v>23501800.92003</v>
+        <v>0.882052280348922</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -8420,10 +8420,10 @@
         <v>9</v>
       </c>
       <c r="C535" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D535">
-        <v>23299971.1828887</v>
+        <v>-0.858784132450396</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -8434,10 +8434,10 @@
         <v>9</v>
       </c>
       <c r="C536" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D536">
-        <v>23572268.2513007</v>
+        <v>1.16865839135445</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -8448,10 +8448,10 @@
         <v>9</v>
       </c>
       <c r="C537" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D537">
-        <v>23912793.681937</v>
+        <v>1.44460188135485</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -8462,10 +8462,10 @@
         <v>9</v>
       </c>
       <c r="C538" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D538">
-        <v>24185244.2763628</v>
+        <v>1.13935075110692</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -8476,10 +8476,10 @@
         <v>9</v>
       </c>
       <c r="C539" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D539">
-        <v>24371790.2623713</v>
+        <v>0.771321487915766</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -8490,10 +8490,10 @@
         <v>9</v>
       </c>
       <c r="C540" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D540">
-        <v>24674037.261043</v>
+        <v>1.24015099185533</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -8504,10 +8504,10 @@
         <v>9</v>
       </c>
       <c r="C541" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D541">
-        <v>24814734.9923674</v>
+        <v>0.570225820103398</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -8518,10 +8518,10 @@
         <v>9</v>
       </c>
       <c r="C542" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D542">
-        <v>24996314.1803144</v>
+        <v>0.731739379859775</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -8532,10 +8532,10 @@
         <v>9</v>
       </c>
       <c r="C543" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D543">
-        <v>25154670.4172205</v>
+        <v>0.633518349000473</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -8546,10 +8546,10 @@
         <v>9</v>
       </c>
       <c r="C544" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D544">
-        <v>25201868.1448844</v>
+        <v>0.187630077759193</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -8560,10 +8560,10 @@
         <v>9</v>
       </c>
       <c r="C545" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D545">
-        <v>25306022.4434135</v>
+        <v>0.41328007086745</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -8574,10 +8574,10 @@
         <v>9</v>
       </c>
       <c r="C546" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D546">
-        <v>25266256.6656595</v>
+        <v>-0.157139581468879</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -8588,10 +8588,10 @@
         <v>9</v>
       </c>
       <c r="C547" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D547">
-        <v>25515285.3375812</v>
+        <v>0.985617597481969</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -8602,10 +8602,10 @@
         <v>9</v>
       </c>
       <c r="C548" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D548">
-        <v>25290826.7955281</v>
+        <v>-0.87970226114813</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -8616,10 +8616,10 @@
         <v>9</v>
       </c>
       <c r="C549" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D549">
-        <v>25486696.256635</v>
+        <v>0.774468397931272</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -8630,10 +8630,10 @@
         <v>9</v>
       </c>
       <c r="C550" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D550">
-        <v>25480578.9853756</v>
+        <v>-0.0240018211768223</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -8644,10 +8644,10 @@
         <v>9</v>
       </c>
       <c r="C551" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D551">
-        <v>25453873.6969464</v>
+        <v>-0.104806442759908</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -8658,10 +8658,10 @@
         <v>9</v>
       </c>
       <c r="C552" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D552">
-        <v>25694485.9522712</v>
+        <v>0.945287378218063</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -8672,10 +8672,10 @@
         <v>9</v>
       </c>
       <c r="C553" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D553">
-        <v>25606452.75203</v>
+        <v>-0.342615144761904</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -8686,10 +8686,10 @@
         <v>9</v>
       </c>
       <c r="C554" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D554">
-        <v>25971192.5814984</v>
+        <v>1.42440592221227</v>
       </c>
     </row>
   </sheetData>
